--- a/contexto/MatrizSeguimientoEvaluacion_20260422_1317.xlsx
+++ b/contexto/MatrizSeguimientoEvaluacion_20260422_1317.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\MEGA\Estudio\python\Seguimiento Regalias\contexto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="11_A78776D1E842DF805D35AEE6E05861D715103029" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A374DD46-2B5A-4085-B2D1-575EA2C15AE1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C34BC8-B0AA-4DF4-9E6B-E87BB4218CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId1"/>
     <sheet name="OtrosEjecutoresDescentralizadas" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId3"/>
-    <sheet name="OtrosEjecutoresMunicipios" sheetId="3" r:id="rId4"/>
+    <sheet name="OtrosEjecutoresMunicipios" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="895">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -1121,9 +1120,6 @@
     <t>Se encuentra en el simulador de la página de Colombia Compra para el proceso de contrataciòn</t>
   </si>
   <si>
-    <t>Proyecto en estado “Sin contratar”, que desde su aprobación presenta 510 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II.</t>
-  </si>
-  <si>
     <t>2024002700176</t>
   </si>
   <si>
@@ -1201,10 +1197,6 @@
   </si>
   <si>
     <t>Contrato de obra contratado El contrato de Interventoría fue declarado desierto. No se ha publicado nuevo proceso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026: El proyecto se encuentra en ejecución  sin acta de inicio desde junio de 2025, el contrato de obra fue adjudicado y suscrito mediante No de contrato LP-009-2025 el 05 de febrero de 2026. Mediante la resolución 0768 del 23 febrero de 2026, se aperturó el proceso CM-002-2026 para la interventorí, Actualmente se encuentra en proceso de evaluación y observaciones.
-Esta situación está generando una calificación de 0, debido a que no se cuenta con programación del proyecto ni con acta de inicio. </t>
   </si>
   <si>
     <t>2024002700184</t>
@@ -1318,9 +1310,6 @@
     <t>Resolución de adjudicación No. 1401 del 8 de abril de 2026 El proceso del contrato de interventoría, sin publicar</t>
   </si>
   <si>
-    <t>20/04/2026: El proyecto cuenta con el primer contrato de consultoría adjudicado el 08 de abril de 2026 y actualmente se encuentra en espera de la firma del contrato, adicionalmente, el proceso precontractual de la interventoría aún no ha sido publicado.</t>
-  </si>
-  <si>
     <t>2025002700021</t>
   </si>
   <si>
@@ -1334,10 +1323,6 @@
 Via terciaria mejorada</t>
   </si>
   <si>
-    <t xml:space="preserve">20/04/2026: Proyecto en estado “Sin contratar”, que desde su aprobación presenta 47 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial
-</t>
-  </si>
-  <si>
     <t>2025002700023</t>
   </si>
   <si>
@@ -1356,9 +1341,6 @@
     <t>Nos permitimos informar que: • El proyecto se encuentra adjudicado desde el 13 de marzo de 2026 y contratado. • Cuenta con Registro Presupuesta (RP) No. 1426 de fecha 27 de marzo de 2026. • Se realizó el pago de las estampillas correspondientes. • Dispone de pólizas requeridas aprobadas. • Se encuentra pendiente la socialización, necesaria para el perfeccionamiento contractual. Una vez surtida la socialización, se procederá con la firma del acta de inicio y el posterior cargue de la programación en la plataforma GESPROY. Se anexan los siguientes documentos: Resolución de adjudicación, Registro Presupuestal, pólizas, soporte de pago de estampillas y pantallazo de aprobación de las pólizas del contrato en secop II.</t>
   </si>
   <si>
-    <t>Proyecto en estado “Contratado sin acta de inicio”, a la espera de la programación inicial y la suscripción del acta de inicio para pasar a estado “en ejecución”. El contrato fue suscrito el 13 de marzo de 2026, por lo cual se debe mantener alerta, teniendo en cuenta que se dispone de 30 días para cargar el acta de inicio y la programación, evitando así una calificación de 0 por parte del DNP.</t>
-  </si>
-  <si>
     <t>2025002700025</t>
   </si>
   <si>
@@ -1380,9 +1362,6 @@
     <t>Nos permitimos informar que: • El contratista realizó el pago de las estampillas correspondientes. • El proyecto ya se encuentra contratado y cuenta con Registro Presupuestal (RP) No. 626 de fecha 4 de febrero de 2026. • Dispone de pólizas requeridas aprobadas. Se está a la espera de la firma del acta de inicio y posterior cargue de la programación en la plataforma de GESPROY. Se anexan los siguientes documentos: Estampillas, Registro Presupuestal, Pólizas del contrato y pantallazo de aprobación de las pólizas del contrato en secop II.</t>
   </si>
   <si>
-    <t>Proyecto en estado “Contratado sin acta de inicio”, a la espera de la programación inicial y la suscripción del acta de inicio para pasar a estado “en ejecución”. El contrato fue suscrito el 04 de febrero  de 2026, por lo cual se debe mantener alerta, teniendo en cuenta que se dispone de 30 días para cargar el acta de inicio y la programación, evitando así una calificación de 0 por parte del DNP.</t>
-  </si>
-  <si>
     <t>2025002700033</t>
   </si>
   <si>
@@ -1401,9 +1380,6 @@
     <t>Resolución de apertura No. 1397 de 8 de abril de 2026, de la Consultoría Aviso de Convocatoria del Proceso No. CM-004-2026 El proceso del contrato de interventoría no se ha publicado</t>
   </si>
   <si>
-    <t>20/04/2026: Resolución de apertura No. 1397 de 8 de abril de 2026,  con  Proceso No. CM-004-2026 de la Consultoría.  El proceso del contrato de interventoría no se ha publicado.</t>
-  </si>
-  <si>
     <t>2025002700035</t>
   </si>
   <si>
@@ -1417,9 +1393,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Se encuentra en el aplicativo Gesproy en estado “SIN CONTRATAR”. Se solicita remitir información actualizada sobre el estado de contratación, la programación de los eventos de participación ciudadana, la modalidad de contratación prevista para cada uno de los procesos contractuales del proyecto, así como la fecha programada para la apertura de cada uno de dichos procesos.</t>
-  </si>
-  <si>
-    <t>20/04/2026: El proyecto cuenta con el proceso de contratación de la consultoría No. CM-003-2026 publicado en SECOP II desde el 13 de febrero de 2026; sin embargo, a la fecha aún no se ha iniciado el proceso de contratación de la interventoría.</t>
   </si>
   <si>
     <t>Mejoramiento en pavimento rígido y construcción de obras hidráulicas en tramos viales en las subregiones Sabana y Montes de María en el departamento de  Sucre</t>
@@ -1436,9 +1409,6 @@
 </t>
   </si>
   <si>
-    <t>20/04/2026: Proyecto en estado “Sin contratar”, que desde su aprobación presenta 47 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial</t>
-  </si>
-  <si>
     <t>EJECUTOR</t>
   </si>
   <si>
@@ -1451,13 +1421,7 @@
     <t>FUENTE</t>
   </si>
   <si>
-    <t xml:space="preserve">VALOR OTROS </t>
-  </si>
-  <si>
     <t>VALOR TOTAL</t>
-  </si>
-  <si>
-    <t>FECHA DE INCORPORACIÓN DE RECUROS</t>
   </si>
   <si>
     <t>AVANCE FÍSICO</t>
@@ -1654,9 +1618,6 @@
     <t>Sin contratar</t>
   </si>
   <si>
-    <t xml:space="preserve">COMENTARIOS </t>
-  </si>
-  <si>
     <t>MUNICIPIO DE MORROA</t>
   </si>
   <si>
@@ -2810,63 +2771,6 @@
     <t>Proyecto terminado pero sigue apareciendo en la plataforma en ejecución</t>
   </si>
   <si>
-    <t>CAMBIO</t>
-  </si>
-  <si>
-    <t>MATRIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGREGAR COLUMNA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPARTAMENTO </t>
-  </si>
-  <si>
-    <t>HORIZONTE EN DESCENTRALIZADAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESPONSABLE DEL PROYECTO </t>
-  </si>
-  <si>
-    <t>DESCENTRALIZADAS</t>
-  </si>
-  <si>
-    <t>TIPO DE CAMBIO</t>
-  </si>
-  <si>
-    <t>AGREGAR CARACTERISTICAS</t>
-  </si>
-  <si>
-    <t>% FÍSICO Y FINANCIERO EN LA TARJETA DE ESTADO DEL PROYECTO</t>
-  </si>
-  <si>
-    <t>PÁGINA REPORTE  SEGUIMIENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVISIÓN </t>
-  </si>
-  <si>
-    <t>REPORTE DE EXCEL</t>
-  </si>
-  <si>
-    <t>AJUSTE</t>
-  </si>
-  <si>
-    <t>CÁLCULO H2</t>
-  </si>
-  <si>
-    <t>AGREGAR LOS MUNICIPIOS</t>
-  </si>
-  <si>
-    <t>AGREGAR LAS DESCENTRALIZADAS</t>
-  </si>
-  <si>
-    <t>01/01/1753</t>
-  </si>
-  <si>
-    <t>29/12/202</t>
-  </si>
-  <si>
     <t>RESPONSABLE CARGUE EN GESPROY</t>
   </si>
   <si>
@@ -2894,11 +2798,50 @@
     <t>OSVALDO SIERRA CARVAJALINO</t>
   </si>
   <si>
-    <t xml:space="preserve">	07/04/2026	</t>
-  </si>
-  <si>
-    <t>20/04/2026: Proyecto en estado “Sin contratar”, que desde su aprobación presenta 34 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II. Se realizó solicitud del CDP, aún no se ha publicado proceso de contratación, están en elaboración de estudios previos.
-27/04/2026: Ya cuenta con CDP, en elaboración de estudios previos</t>
+    <t xml:space="preserve">
+05/05/2026: El 4 de mayo de 2026 se suscribió el contrato de obra. En cuanto al proceso para la contratación de la interventoría, el 24 de abril 2026 se radicaron en la oficina de subcontratación los estudios previos y demás documentación soporte, para su respectiva revisión y trámite; actualmente, se encuentra a la espera de la publicación del respectivo proceso contractual. Este proyecto debería aparecer en Gesproy "contratado sin acta de inicio", sin embargo, está a la espera de que migre el contrato a la plataforma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+05/05/2026: Mediante la Resolución No. 1786 del 30 de abril de 2026, se adjudicó el Contrato No. CM-004-2026, no obstante, a la fecha no se ha suscrito el contrato correspondiente.
+En cuanto al proceso para la contratación de la interventoría, el día 24 de abril se radicaron en la oficina de subcontratación los estudios previos y demás documentación soporte, para su respectiva revisión y trámite. Actualmente, se encuentra a la espera de la publicación del respectivo proceso contractual.</t>
+  </si>
+  <si>
+    <t>05/05/2026 : El proyecto cuenta con el proceso de contratación de la consultoría No. CM-003-2026 publicado en SECOP II desde el 13 de febrero de 2026; sin embargo, a la fecha aún no se ha iniciado el proceso de contratación de la interventoría,  Se prevee que entre el 08 de mayo y 10 de mayo se aperture el proceso de contratación de la interventoría.</t>
+  </si>
+  <si>
+    <t>05/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026: El proyecto se encuentra en ejecución  sin acta de inicio desde junio de 2025, el contrato de obra fue adjudicado y suscrito mediante No de contrato LP-009-2025 el 05 de febrero de 2026. Mediante la resolución 0768 del 23 febrero de 2026, se aperturó el proceso CM-002-2026 para la interventoría, Actualmente se encuentra en proceso de evaluación y observaciones.
+Esta situación está generando una calificación de 0, debido a que no se cuenta con programación del proyecto ni con acta de inicio. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026: Proyecto en estado “Contratado sin acta de inicio”, a la espera de la programación inicial y la suscripción del acta de inicio para pasar a estado “en ejecución”. El contrato fue suscrito el 04 de febrero  de 2026, por lo cual se debe mantener alerta, teniendo en cuenta que se dispone de 30 días para cargar el acta de inicio y la programación, evitando así una calificación de 0 por parte del DNP.
+Conforme a lo informado por la sectorial, se requiere la modificación de una cláusula del convenio, en atención a ciertos requisitos que deben cumplirse previamente a la suscripción del acta de inicio. En consecuencia, se hace necesario la elaboración de un otrosí, el cual se prevé suscribir entre el 7 y el 9 de mayo, con el fin de proceder posteriormente a la firma del acta de inicio.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+05/05/2026: El proyecto ya cuenta con acta de inicio y programación inicial, las cuales serán cargadas en la plataforma Gesproy para su cambio al estado ‘En ejecución’. En consecuencia, el proyecto deja de presentar alerta por falta de acta  inicio.</t>
+  </si>
+  <si>
+    <t>COMENTARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II, cuenta con CDP, en elaboración de estudios previos por parte de la sectorial.
+</t>
+  </si>
+  <si>
+    <t>13/05/2026: Proyecto realizó apertura de proceso de simulación en Colombia compra eficiente  de la  compra de maquinaria amarilla-agrícola (5-marzo de 2026), este proceso fue declarado desierto.
+Conforme a la información proporcionada por la sectorial ya fueron radicados nuevamente  los estudios previos  a contratación el 04/05/2026</t>
+  </si>
+  <si>
+    <t>2025000020006</t>
   </si>
 </sst>
 </file>
@@ -2910,7 +2853,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2955,6 +2898,19 @@
       <sz val="10"/>
       <name val="Roboto"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3037,7 +2993,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3068,40 +3024,16 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3139,22 +3071,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3172,10 +3089,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3187,13 +3101,25 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3201,6 +3127,100 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3859,100 +3879,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Roboto"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Roboto"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3968,13 +3894,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AW58" totalsRowShown="0">
-  <autoFilter ref="A2:AW58" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="PARA CIERRE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:AW58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="49">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -4024,7 +3944,7 @@
     <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="COLUMNA APOYO 2"/>
     <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO"/>
     <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN"/>
-    <tableColumn id="49" xr3:uid="{13FEDD79-59CD-4A59-97F8-8DE831491970}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="22"/>
+    <tableColumn id="49" xr3:uid="{13FEDD79-59CD-4A59-97F8-8DE831491970}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4043,13 +3963,13 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="ESTADO PROYECTO"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="ESTADO CONTRATO"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="VALOR SGR"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS "/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VALOR TOTAL"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="FECHA DE MIGRACIÓN A GESPROY"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS" dataDxfId="21">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS" dataDxfId="2">
       <calculatedColumnFormula>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS" dataDxfId="1"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="CPI"/>
@@ -4058,7 +3978,7 @@
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="FECHA ACTA INICIO"/>
-    <tableColumn id="38" xr3:uid="{29D10468-846C-4252-8639-4B1971D4562B}" name="HORIZONTE DEL PROYECTO" dataDxfId="19"/>
+    <tableColumn id="38" xr3:uid="{29D10468-846C-4252-8639-4B1971D4562B}" name="HORIZONTE DEL PROYECTO" dataDxfId="0"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="FECHA DE CORTE GESPROY"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="DIAS DESDE LA APROBACIÓN HASTA APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="DIAS DESDE LA APERTURA HASTA LA FIRMA DEL PRIMER CONTRATO"/>
@@ -4080,27 +4000,27 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OtrosEjecutoresMunicipios" displayName="OtrosEjecutoresMunicipios" ref="A2:R104" totalsRowShown="0" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OtrosEjecutoresMunicipios" displayName="OtrosEjecutoresMunicipios" ref="A2:R104" totalsRowShown="0" dataDxfId="22">
   <autoFilter ref="A2:R104" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="BPIN" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="EJECUTOR" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="NOMBRE DEL PROYECTO" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ALCANCE" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="SECTOR" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="FUENTE" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="ESTADO PROYECTO" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="ESTADO CONTRATO" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="VALOR SGR" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="VALOR OTROS" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="VALOR TOTAL" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="FECHA APROBACIÓN PROYECTO" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="FECHA ACTA INICIO" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO" dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS " dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="BPIN" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="EJECUTOR" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="NOMBRE DEL PROYECTO" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ALCANCE" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="SECTOR" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="FUENTE" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="ESTADO PROYECTO" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="ESTADO CONTRATO" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="VALOR SGR" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="VALOR OTROS" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="VALOR TOTAL" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="FECHA APROBACIÓN PROYECTO" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="FECHA ACTA INICIO" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4394,82 +4314,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
-    <col min="4" max="4" width="46.28515625" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" customWidth="1"/>
-    <col min="6" max="6" width="43.28515625" customWidth="1"/>
-    <col min="7" max="31" width="25.7109375" customWidth="1"/>
-    <col min="32" max="32" width="56.7109375" customWidth="1"/>
-    <col min="33" max="33" width="34.28515625" customWidth="1"/>
-    <col min="34" max="34" width="25.7109375" customWidth="1"/>
-    <col min="35" max="44" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="25.7109375" customWidth="1"/>
-    <col min="46" max="46" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="25.7109375" customWidth="1"/>
-    <col min="48" max="48" width="33" customWidth="1"/>
-    <col min="49" max="49" width="29.28515625" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" customWidth="1"/>
+    <col min="4" max="4" width="46.33203125" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" customWidth="1"/>
+    <col min="7" max="31" width="25.6640625" customWidth="1"/>
+    <col min="32" max="32" width="56.6640625" customWidth="1"/>
+    <col min="33" max="33" width="34.33203125" customWidth="1"/>
+    <col min="34" max="47" width="25.6640625" customWidth="1"/>
+    <col min="48" max="48" width="42.33203125" customWidth="1"/>
+    <col min="49" max="49" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="32" t="s">
+    <row r="1" spans="1:49" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="31" t="s">
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="31"/>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
+      <c r="AR1" s="28"/>
+      <c r="AS1" s="28"/>
+      <c r="AT1" s="28"/>
+      <c r="AU1" s="28"/>
+      <c r="AV1" s="28"/>
     </row>
-    <row r="2" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -4614,11 +4530,11 @@
       <c r="AV2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AW2" s="30" t="s">
-        <v>906</v>
+      <c r="AW2" s="22" t="s">
+        <v>875</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="112.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
@@ -4748,11 +4664,11 @@
       <c r="AV3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AW3" s="26" t="s">
-        <v>912</v>
+      <c r="AW3" s="19" t="s">
+        <v>881</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -4882,11 +4798,11 @@
       <c r="AV4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AW4" s="25" t="s">
-        <v>907</v>
+      <c r="AW4" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>72</v>
       </c>
@@ -5026,11 +4942,11 @@
       <c r="AV5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW5" s="25" t="s">
-        <v>907</v>
+      <c r="AW5" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>80</v>
       </c>
@@ -5172,11 +5088,11 @@
       <c r="AV6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AW6" s="25" t="s">
-        <v>907</v>
+      <c r="AW6" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="141.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>88</v>
       </c>
@@ -5316,11 +5232,11 @@
       <c r="AV7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AW7" s="25" t="s">
-        <v>908</v>
+      <c r="AW7" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>99</v>
       </c>
@@ -5452,11 +5368,11 @@
       <c r="AV8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AW8" s="26" t="s">
-        <v>912</v>
+      <c r="AW8" s="19" t="s">
+        <v>881</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="156.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -5600,11 +5516,11 @@
       <c r="AV9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AW9" s="25" t="s">
-        <v>907</v>
+      <c r="AW9" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>113</v>
       </c>
@@ -5744,11 +5660,11 @@
       <c r="AV10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW10" s="25" t="s">
-        <v>909</v>
+      <c r="AW10" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>119</v>
       </c>
@@ -5888,11 +5804,11 @@
       <c r="AV11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW11" s="25" t="s">
-        <v>907</v>
+      <c r="AW11" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>124</v>
       </c>
@@ -6032,11 +5948,11 @@
       <c r="AV12" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW12" s="25" t="s">
-        <v>909</v>
+      <c r="AW12" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>132</v>
       </c>
@@ -6178,11 +6094,11 @@
       <c r="AV13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AW13" s="25" t="s">
-        <v>910</v>
+      <c r="AW13" s="18" t="s">
+        <v>879</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>142</v>
       </c>
@@ -6322,11 +6238,11 @@
       <c r="AV14" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="AW14" s="25" t="s">
-        <v>908</v>
+      <c r="AW14" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>149</v>
       </c>
@@ -6468,11 +6384,11 @@
       <c r="AV15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AW15" s="25" t="s">
-        <v>907</v>
+      <c r="AW15" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>155</v>
       </c>
@@ -6612,11 +6528,11 @@
       <c r="AV16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW16" s="25" t="s">
-        <v>909</v>
+      <c r="AW16" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>161</v>
       </c>
@@ -6758,11 +6674,11 @@
       <c r="AV17" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="AW17" s="25" t="s">
-        <v>909</v>
+      <c r="AW17" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>169</v>
       </c>
@@ -6904,11 +6820,11 @@
       <c r="AV18" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AW18" s="25" t="s">
-        <v>907</v>
+      <c r="AW18" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="19" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>176</v>
       </c>
@@ -7050,11 +6966,11 @@
       <c r="AV19" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AW19" s="25" t="s">
-        <v>907</v>
+      <c r="AW19" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="20" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>181</v>
       </c>
@@ -7194,11 +7110,11 @@
       <c r="AV20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW20" s="25" t="s">
-        <v>907</v>
+      <c r="AW20" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>186</v>
       </c>
@@ -7340,11 +7256,11 @@
       <c r="AV21" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AW21" s="25" t="s">
-        <v>911</v>
+      <c r="AW21" s="18" t="s">
+        <v>880</v>
       </c>
     </row>
-    <row r="22" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>195</v>
       </c>
@@ -7486,11 +7402,11 @@
       <c r="AV22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AW22" s="25" t="s">
-        <v>912</v>
+      <c r="AW22" s="18" t="s">
+        <v>881</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>203</v>
       </c>
@@ -7622,11 +7538,11 @@
       <c r="AV23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW23" s="25" t="s">
-        <v>908</v>
+      <c r="AW23" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>209</v>
       </c>
@@ -7758,11 +7674,11 @@
       <c r="AV24" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AW24" s="25" t="s">
-        <v>907</v>
+      <c r="AW24" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="25" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>217</v>
       </c>
@@ -7896,11 +7812,11 @@
       <c r="AV25" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW25" s="25" t="s">
-        <v>907</v>
+      <c r="AW25" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="26" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>222</v>
       </c>
@@ -8042,11 +7958,11 @@
       <c r="AV26" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="AW26" s="25" t="s">
-        <v>909</v>
+      <c r="AW26" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>229</v>
       </c>
@@ -8186,18 +8102,18 @@
       <c r="AV27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW27" s="25" t="s">
-        <v>912</v>
+      <c r="AW27" s="18" t="s">
+        <v>881</v>
       </c>
     </row>
-    <row r="28" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="23" t="s">
         <v>236</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -8322,11 +8238,11 @@
       <c r="AV28" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW28" s="25" t="s">
-        <v>908</v>
+      <c r="AW28" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="29" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>239</v>
       </c>
@@ -8466,11 +8382,11 @@
       <c r="AV29" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="AW29" s="25" t="s">
-        <v>909</v>
+      <c r="AW29" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="30" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>246</v>
       </c>
@@ -8602,11 +8518,11 @@
       <c r="AV30" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW30" s="25" t="s">
-        <v>909</v>
+      <c r="AW30" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="31" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>250</v>
       </c>
@@ -8746,11 +8662,11 @@
       <c r="AV31" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="AW31" s="25" t="s">
-        <v>908</v>
+      <c r="AW31" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="32" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>258</v>
       </c>
@@ -8892,11 +8808,11 @@
       <c r="AV32" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="AW32" s="25" t="s">
-        <v>908</v>
+      <c r="AW32" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="33" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>266</v>
       </c>
@@ -9038,11 +8954,11 @@
       <c r="AV33" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="AW33" s="25" t="s">
-        <v>909</v>
+      <c r="AW33" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="34" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>275</v>
       </c>
@@ -9174,11 +9090,11 @@
       <c r="AV34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW34" s="25" t="s">
-        <v>908</v>
+      <c r="AW34" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="35" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>280</v>
       </c>
@@ -9308,11 +9224,11 @@
       <c r="AV35" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW35" s="25" t="s">
-        <v>907</v>
+      <c r="AW35" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="36" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>285</v>
       </c>
@@ -9452,11 +9368,11 @@
       <c r="AV36" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AW36" s="25" t="s">
-        <v>909</v>
+      <c r="AW36" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="37" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>292</v>
       </c>
@@ -9598,11 +9514,11 @@
       <c r="AV37" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AW37" s="25" t="s">
-        <v>907</v>
+      <c r="AW37" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="38" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>299</v>
       </c>
@@ -9744,11 +9660,11 @@
       <c r="AV38" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AW38" s="25" t="s">
-        <v>908</v>
+      <c r="AW38" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="39" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>307</v>
       </c>
@@ -9888,11 +9804,11 @@
       <c r="AV39" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="AW39" s="25" t="s">
-        <v>907</v>
+      <c r="AW39" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="40" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>314</v>
       </c>
@@ -10034,11 +9950,11 @@
       <c r="AV40" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="AW40" s="25" t="s">
-        <v>908</v>
+      <c r="AW40" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="41" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>320</v>
       </c>
@@ -10180,11 +10096,11 @@
       <c r="AV41" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="AW41" s="25" t="s">
-        <v>909</v>
+      <c r="AW41" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="42" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>327</v>
       </c>
@@ -10324,11 +10240,11 @@
       <c r="AV42" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="AW42" s="25" t="s">
-        <v>912</v>
+      <c r="AW42" s="18" t="s">
+        <v>881</v>
       </c>
     </row>
-    <row r="43" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:49" ht="183.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>332</v>
       </c>
@@ -10394,7 +10310,9 @@
       <c r="Y43" s="5">
         <v>45615</v>
       </c>
-      <c r="Z43" s="5"/>
+      <c r="Z43" s="5">
+        <v>46086</v>
+      </c>
       <c r="AA43" s="5"/>
       <c r="AB43" s="5"/>
       <c r="AC43" s="5"/>
@@ -10454,30 +10372,30 @@
         <v/>
       </c>
       <c r="AV43" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="AW43" s="18" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="44" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="AW43" s="25" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="44" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>267</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>270</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>68</v>
@@ -10553,10 +10471,10 @@
         <v>46127</v>
       </c>
       <c r="AF44" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="AG44" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="AG44" s="3" t="s">
-        <v>345</v>
       </c>
       <c r="AH44" s="5">
         <v>46122</v>
@@ -10600,30 +10518,30 @@
         <v>36</v>
       </c>
       <c r="AV44" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AW44" s="18" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="45" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="AW44" s="25" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="45" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>347</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>68</v>
@@ -10632,10 +10550,10 @@
         <v>84</v>
       </c>
       <c r="I45" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>353</v>
       </c>
       <c r="K45" s="4">
         <v>1135083847</v>
@@ -10697,10 +10615,10 @@
         <v>46127</v>
       </c>
       <c r="AF45" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="AG45" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="AH45" s="5">
         <v>46126</v>
@@ -10744,42 +10662,42 @@
         <v>60</v>
       </c>
       <c r="AV45" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="AW45" s="18" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="46" spans="1:49" ht="177.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="AW45" s="25" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="46" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>212</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>159</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K46" s="4">
         <v>2439637568.0900002</v>
@@ -10835,10 +10753,10 @@
         <v>46127</v>
       </c>
       <c r="AF46" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="AG46" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="AG46" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="AH46" s="5">
         <v>46126</v>
@@ -10886,30 +10804,30 @@
         <v/>
       </c>
       <c r="AV46" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="AW46" s="25" t="s">
-        <v>909</v>
+        <v>888</v>
+      </c>
+      <c r="AW46" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="47" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>68</v>
@@ -10918,7 +10836,7 @@
         <v>84</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>95</v>
@@ -10985,10 +10903,10 @@
         <v>46127</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG47" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AH47" s="5">
         <v>46126</v>
@@ -11032,21 +10950,21 @@
         <v>86.4</v>
       </c>
       <c r="AV47" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="AW47" s="25" t="s">
-        <v>909</v>
+        <v>371</v>
+      </c>
+      <c r="AW47" s="18" t="s">
+        <v>878</v>
       </c>
     </row>
-    <row r="48" spans="1:49" ht="114.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>2025000020006</v>
+    <row r="48" spans="1:49" ht="154.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
+        <v>894</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3" t="s">
@@ -11148,42 +11066,42 @@
         <v/>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="AW48" s="25" t="s">
-        <v>907</v>
+        <v>892</v>
+      </c>
+      <c r="AW48" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="49" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>159</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K49" s="4">
         <v>15884181916</v>
@@ -11243,10 +11161,10 @@
         <v>46127</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG49" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AH49" s="5">
         <v>46127</v>
@@ -11290,30 +11208,30 @@
         <v>40</v>
       </c>
       <c r="AV49" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="AW49" s="25" t="s">
-        <v>907</v>
+        <v>380</v>
+      </c>
+      <c r="AW49" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="50" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>68</v>
@@ -11322,7 +11240,7 @@
         <v>84</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>165</v>
@@ -11387,10 +11305,10 @@
         <v>46127</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG50" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AH50" s="5">
         <v>46126</v>
@@ -11434,24 +11352,24 @@
         <v>100</v>
       </c>
       <c r="AV50" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="AW50" s="25" t="s">
-        <v>913</v>
+        <v>387</v>
+      </c>
+      <c r="AW50" s="18" t="s">
+        <v>882</v>
       </c>
     </row>
-    <row r="51" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:49" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>278</v>
@@ -11533,10 +11451,10 @@
         <v>46127</v>
       </c>
       <c r="AF51" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AG51" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AH51" s="5">
         <v>46122</v>
@@ -11580,30 +11498,30 @@
         <v>100</v>
       </c>
       <c r="AV51" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="AW51" s="25" t="s">
-        <v>913</v>
+        <v>387</v>
+      </c>
+      <c r="AW51" s="18" t="s">
+        <v>882</v>
       </c>
     </row>
-    <row r="52" spans="1:49" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:49" ht="249" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>336</v>
@@ -11663,10 +11581,10 @@
         <v>46127</v>
       </c>
       <c r="AF52" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG52" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AH52" s="5">
         <v>46126</v>
@@ -11713,31 +11631,31 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV52" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="AW52" s="25" t="s">
-        <v>913</v>
+      <c r="AV52" s="26" t="s">
+        <v>883</v>
+      </c>
+      <c r="AW52" s="18" t="s">
+        <v>882</v>
       </c>
     </row>
-    <row r="53" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:49" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>336</v>
@@ -11836,39 +11754,39 @@
         <v/>
       </c>
       <c r="AV53" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="AW53" s="25" t="s">
-        <v>907</v>
+        <v>884</v>
+      </c>
+      <c r="AW53" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
-    <row r="54" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:49" ht="179.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>267</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>270</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G54" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="I54" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>95</v>
@@ -11925,10 +11843,10 @@
         <v>46127</v>
       </c>
       <c r="AF54" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AG54" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AH54" s="5">
         <v>46122</v>
@@ -11976,42 +11894,42 @@
         <v/>
       </c>
       <c r="AV54" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="AW54" s="25" t="s">
-        <v>913</v>
+        <v>890</v>
+      </c>
+      <c r="AW54" s="18" t="s">
+        <v>882</v>
       </c>
     </row>
-    <row r="55" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:49" ht="254.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>267</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>270</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="G55" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="I55" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="K55" s="4">
         <v>1631281390</v>
@@ -12065,10 +11983,10 @@
         <v>46127</v>
       </c>
       <c r="AF55" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AG55" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AH55" s="5">
         <v>46122</v>
@@ -12115,31 +12033,31 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV55" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="AW55" s="25" t="s">
-        <v>913</v>
+      <c r="AV55" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="AW55" s="18" t="s">
+        <v>882</v>
       </c>
     </row>
-    <row r="56" spans="1:49" ht="199.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:49" ht="244.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>336</v>
@@ -12147,7 +12065,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="K56" s="10">
         <v>2998247290</v>
@@ -12199,10 +12117,10 @@
         <v>46127</v>
       </c>
       <c r="AF56" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG56" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AH56" s="5">
         <v>46126</v>
@@ -12250,30 +12168,30 @@
         <v/>
       </c>
       <c r="AV56" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="AW56" s="25" t="s">
-        <v>913</v>
+        <v>885</v>
+      </c>
+      <c r="AW56" s="18" t="s">
+        <v>882</v>
       </c>
     </row>
-    <row r="57" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:49" ht="143.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>212</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>336</v>
@@ -12281,7 +12199,7 @@
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="K57" s="10">
         <v>4190286255</v>
@@ -12302,9 +12220,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="5"/>
-      <c r="R57" s="5">
-        <v>0</v>
-      </c>
+      <c r="R57" s="5"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
         <v>46017</v>
@@ -12331,7 +12247,7 @@
         <v>46127</v>
       </c>
       <c r="AF57" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="AG57" s="3"/>
       <c r="AH57" s="5">
@@ -12380,30 +12296,30 @@
         <v/>
       </c>
       <c r="AV57" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="AW57" s="25" t="s">
-        <v>908</v>
+        <v>886</v>
+      </c>
+      <c r="AW57" s="18" t="s">
+        <v>877</v>
       </c>
     </row>
-    <row r="58" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="29">
+    <row r="58" spans="1:49" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="21">
         <v>2026002700001</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>336</v>
@@ -12411,7 +12327,7 @@
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="K58" s="10">
         <v>15410127474</v>
@@ -12500,10 +12416,10 @@
         <v/>
       </c>
       <c r="AV58" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="AW58" s="27" t="s">
-        <v>907</v>
+        <v>887</v>
+      </c>
+      <c r="AW58" s="18" t="s">
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -12522,82 +12438,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AL18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" customWidth="1"/>
-    <col min="4" max="4" width="37.28515625" customWidth="1"/>
-    <col min="5" max="29" width="25.7109375" customWidth="1"/>
-    <col min="30" max="30" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="31" max="35" width="25.7109375" customWidth="1"/>
-    <col min="36" max="36" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="37" max="38" width="25.7109375" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" customWidth="1"/>
+    <col min="5" max="29" width="25.6640625" customWidth="1"/>
+    <col min="30" max="30" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="35" width="25.6640625" customWidth="1"/>
+    <col min="36" max="36" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="37" max="38" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="32" t="s">
+    <row r="1" spans="1:38" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="31" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
     </row>
-    <row r="2" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -12609,10 +12525,10 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>444</v>
+        <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>20</v>
@@ -12621,10 +12537,10 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>446</v>
+        <v>22</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>24</v>
@@ -12696,30 +12612,30 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I3" s="4">
         <v>2006938345.6700001</v>
@@ -12737,7 +12653,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44197</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="13">
         <v>44326</v>
       </c>
       <c r="O3" s="4">
@@ -12798,33 +12714,33 @@
         <v/>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I4" s="4">
         <v>1295118639.0699999</v>
@@ -12842,7 +12758,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44197</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="13">
         <v>44326</v>
       </c>
       <c r="O4" s="4">
@@ -12903,21 +12819,21 @@
         <v/>
       </c>
       <c r="AL4" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="156" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>2021000020028</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>55</v>
@@ -12929,7 +12845,7 @@
         <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I5" s="4">
         <v>3153851580.9099998</v>
@@ -12947,9 +12863,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44568</v>
       </c>
-      <c r="N5" s="19" t="s">
-        <v>904</v>
-      </c>
+      <c r="N5" s="24"/>
       <c r="O5" s="4">
         <v>96.02</v>
       </c>
@@ -13019,30 +12933,30 @@
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="I6" s="4">
         <v>6026477761</v>
@@ -13060,7 +12974,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44624</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="13">
         <v>44509</v>
       </c>
       <c r="O6" s="4">
@@ -13129,33 +13043,33 @@
         <v>20</v>
       </c>
       <c r="AL6" s="3" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>20221301010208</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I7" s="4">
         <v>1800000000</v>
@@ -13173,7 +13087,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44925</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="13">
         <v>44930</v>
       </c>
       <c r="O7" s="4">
@@ -13242,21 +13156,21 @@
         <v>20</v>
       </c>
       <c r="AL7" s="3" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>55</v>
@@ -13268,7 +13182,7 @@
         <v>57</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I8" s="4">
         <v>1702007732.2</v>
@@ -13286,7 +13200,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45226</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="13">
         <v>45232</v>
       </c>
       <c r="O8" s="4">
@@ -13347,33 +13261,33 @@
         <v/>
       </c>
       <c r="AL8" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" ht="93" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I9" s="4">
         <v>13713002364.719999</v>
@@ -13391,7 +13305,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45302</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="13">
         <v>45290</v>
       </c>
       <c r="O9" s="4">
@@ -13456,21 +13370,21 @@
         <v/>
       </c>
       <c r="AL9" s="3" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>220</v>
@@ -13482,7 +13396,7 @@
         <v>68</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I10" s="4">
         <v>9056051736.6399994</v>
@@ -13500,7 +13414,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45302</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="13">
         <v>45290</v>
       </c>
       <c r="O10" s="4">
@@ -13568,18 +13482,18 @@
       </c>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>278</v>
@@ -13591,7 +13505,7 @@
         <v>68</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I11" s="4">
         <v>7862105021</v>
@@ -13609,7 +13523,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45478</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="13">
         <v>45485</v>
       </c>
       <c r="O11" s="4">
@@ -13679,18 +13593,18 @@
       </c>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:38" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>253</v>
@@ -13702,7 +13616,7 @@
         <v>68</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I12" s="4">
         <v>15100656106.639999</v>
@@ -13720,7 +13634,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45475</v>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="13">
         <v>45506</v>
       </c>
       <c r="O12" s="4">
@@ -13789,21 +13703,21 @@
         <v>36</v>
       </c>
       <c r="AL12" s="3" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>270</v>
@@ -13815,7 +13729,7 @@
         <v>68</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I13" s="4">
         <v>3068416428</v>
@@ -13833,7 +13747,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45659</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="13">
         <v>45656</v>
       </c>
       <c r="O13" s="4">
@@ -13901,18 +13815,18 @@
       </c>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2024002700193</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>253</v>
@@ -13924,7 +13838,7 @@
         <v>68</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I14" s="4">
         <v>63850574205.629997</v>
@@ -13942,7 +13856,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45659</v>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="13">
         <v>45656</v>
       </c>
       <c r="O14" s="4">
@@ -14012,18 +13926,18 @@
       </c>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>278</v>
@@ -14035,7 +13949,7 @@
         <v>68</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I15" s="4">
         <v>11318403530.17</v>
@@ -14053,7 +13967,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45823</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="13">
         <v>45825</v>
       </c>
       <c r="O15" s="4">
@@ -14121,18 +14035,18 @@
       </c>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>253</v>
@@ -14141,10 +14055,10 @@
         <v>215</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="I16" s="4">
         <v>1903272161</v>
@@ -14162,7 +14076,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45790</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="13">
         <v>45803</v>
       </c>
       <c r="O16" s="4">
@@ -14228,18 +14142,18 @@
       </c>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>253</v>
@@ -14251,7 +14165,7 @@
         <v>68</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I17" s="4">
         <v>1484402616</v>
@@ -14263,11 +14177,8 @@
         <v>1884402616</v>
       </c>
       <c r="L17" s="5"/>
-      <c r="M17" s="5">
-        <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
-        <v>1</v>
-      </c>
-      <c r="N17" s="19">
+      <c r="M17" s="5"/>
+      <c r="N17" s="13">
         <v>45803</v>
       </c>
       <c r="O17" s="4">
@@ -14335,30 +14246,30 @@
       </c>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="144" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>336</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="I18" s="4">
         <v>627486059.86000001</v>
@@ -14376,8 +14287,8 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>46119</v>
       </c>
-      <c r="N18" s="28" t="s">
-        <v>914</v>
+      <c r="N18" s="20">
+        <v>46119</v>
       </c>
       <c r="O18" s="4">
         <v>0</v>
@@ -14452,152 +14363,55 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41BB839-CD8D-4F7F-BBA8-C26EF6962443}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:R104"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" customWidth="1"/>
+    <col min="4" max="18" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>894</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>887</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>888</v>
-      </c>
+    <row r="1" spans="1:18" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>889</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>892</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>889</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>891</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>895</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>896</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>898</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>899</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>900</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>901</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>900</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>900</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>903</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" customWidth="1"/>
-    <col min="4" max="18" width="25.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-    </row>
-    <row r="2" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -14612,7 +14426,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>27</v>
@@ -14621,33 +14435,33 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>446</v>
+        <v>22</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>508</v>
+        <v>891</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2012000020042</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>92</v>
@@ -14659,7 +14473,7 @@
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I3" s="4">
         <v>22526692745</v>
@@ -14670,14 +14484,14 @@
       <c r="K3" s="4">
         <v>22526692745</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="13">
         <v>41201</v>
       </c>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19">
+      <c r="M3" s="13"/>
+      <c r="N3" s="13">
         <v>41829</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="13">
         <v>42072</v>
       </c>
       <c r="P3" s="4">
@@ -14688,18 +14502,18 @@
       </c>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>2012002700005</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>92</v>
@@ -14710,8 +14524,8 @@
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>453</v>
+      <c r="H4" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I4" s="4">
         <v>924979909</v>
@@ -14722,14 +14536,14 @@
       <c r="K4" s="4">
         <v>954979909</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="13">
         <v>41191</v>
       </c>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19">
+      <c r="M4" s="13"/>
+      <c r="N4" s="13">
         <v>41304</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="13">
         <v>41452</v>
       </c>
       <c r="P4" s="4">
@@ -14740,18 +14554,18 @@
       </c>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>92</v>
@@ -14763,7 +14577,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I5" s="4">
         <v>999998309</v>
@@ -14774,14 +14588,14 @@
       <c r="K5" s="4">
         <v>1010998309</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="13">
         <v>41191</v>
       </c>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19">
+      <c r="M5" s="13"/>
+      <c r="N5" s="13">
         <v>41276</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="13">
         <v>41355</v>
       </c>
       <c r="P5" s="4">
@@ -14792,18 +14606,18 @@
       </c>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>92</v>
@@ -14815,7 +14629,7 @@
         <v>57</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I6" s="4">
         <v>16567304387</v>
@@ -14826,14 +14640,14 @@
       <c r="K6" s="4">
         <v>16567304387</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="13">
         <v>41533</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19">
+      <c r="M6" s="13"/>
+      <c r="N6" s="13">
         <v>41537</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="13">
         <v>41669</v>
       </c>
       <c r="P6" s="4">
@@ -14844,30 +14658,30 @@
       </c>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>453</v>
+      <c r="H7" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I7" s="4">
         <v>12429000000</v>
@@ -14878,14 +14692,14 @@
       <c r="K7" s="4">
         <v>12588110083</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="13">
         <v>41907</v>
       </c>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19">
+      <c r="M7" s="13"/>
+      <c r="N7" s="13">
         <v>42821</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="13">
         <v>42226</v>
       </c>
       <c r="P7" s="4">
@@ -14896,21 +14710,21 @@
       </c>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>60</v>
@@ -14918,8 +14732,8 @@
       <c r="G8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>467</v>
+      <c r="H8" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I8" s="4">
         <v>14996018261</v>
@@ -14930,14 +14744,14 @@
       <c r="K8" s="4">
         <v>14996018261</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="13">
         <v>41376</v>
       </c>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19">
+      <c r="M8" s="13"/>
+      <c r="N8" s="13">
         <v>41380</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="13">
         <v>41676</v>
       </c>
       <c r="P8" s="4">
@@ -14948,30 +14762,30 @@
       </c>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>462</v>
+      <c r="H9" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I9" s="4">
         <v>14913362760</v>
@@ -14982,14 +14796,14 @@
       <c r="K9" s="4">
         <v>14913362760</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="13">
         <v>41907</v>
       </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19">
+      <c r="M9" s="13"/>
+      <c r="N9" s="13">
         <v>42990</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="13">
         <v>42023</v>
       </c>
       <c r="P9" s="4">
@@ -15000,30 +14814,30 @@
       </c>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="22" t="s">
-        <v>453</v>
+      <c r="H10" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I10" s="4">
         <v>7037696704</v>
@@ -15034,14 +14848,14 @@
       <c r="K10" s="4">
         <v>7738617014</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="13">
         <v>41907</v>
       </c>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19">
+      <c r="M10" s="13"/>
+      <c r="N10" s="13">
         <v>42006</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="13">
         <v>42060</v>
       </c>
       <c r="P10" s="4">
@@ -15052,18 +14866,18 @@
       </c>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>66</v>
@@ -15075,7 +14889,7 @@
         <v>57</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I11" s="4">
         <v>13800000000</v>
@@ -15086,14 +14900,14 @@
       <c r="K11" s="4">
         <v>15951400000</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="13">
         <v>41789</v>
       </c>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19">
+      <c r="M11" s="13"/>
+      <c r="N11" s="13">
         <v>44936</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="13">
         <v>42128</v>
       </c>
       <c r="P11" s="4">
@@ -15104,30 +14918,30 @@
       </c>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>453</v>
+      <c r="H12" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I12" s="4">
         <v>16094650077</v>
@@ -15138,14 +14952,14 @@
       <c r="K12" s="4">
         <v>16407417777</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="13">
         <v>43389</v>
       </c>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19">
+      <c r="M12" s="13"/>
+      <c r="N12" s="13">
         <v>43495</v>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="13">
         <v>43865</v>
       </c>
       <c r="P12" s="4">
@@ -15156,30 +14970,30 @@
       </c>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="I13" s="4">
         <v>54337268559</v>
@@ -15190,14 +15004,14 @@
       <c r="K13" s="4">
         <v>62896276985</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="13">
         <v>43165</v>
       </c>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19">
+      <c r="M13" s="13"/>
+      <c r="N13" s="13">
         <v>43171</v>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="13">
         <v>43410</v>
       </c>
       <c r="P13" s="4">
@@ -15208,30 +15022,30 @@
       </c>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>453</v>
+      <c r="H14" s="16" t="s">
+        <v>442</v>
       </c>
       <c r="I14" s="4">
         <v>5261488233</v>
@@ -15242,14 +15056,14 @@
       <c r="K14" s="4">
         <v>5361488233</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="13">
         <v>43636</v>
       </c>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19">
+      <c r="M14" s="13"/>
+      <c r="N14" s="13">
         <v>43955</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="13">
         <v>44138</v>
       </c>
       <c r="P14" s="4">
@@ -15260,18 +15074,18 @@
       </c>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>135</v>
@@ -15282,8 +15096,8 @@
       <c r="G15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>453</v>
+      <c r="H15" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I15" s="4">
         <v>8077068482</v>
@@ -15294,14 +15108,14 @@
       <c r="K15" s="4">
         <v>8077068482</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="13">
         <v>43829</v>
       </c>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19">
+      <c r="M15" s="13"/>
+      <c r="N15" s="13">
         <v>43843</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="13">
         <v>44042</v>
       </c>
       <c r="P15" s="4">
@@ -15312,18 +15126,18 @@
       </c>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>66</v>
@@ -15335,7 +15149,7 @@
         <v>68</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I16" s="4">
         <v>7750000000</v>
@@ -15346,14 +15160,14 @@
       <c r="K16" s="4">
         <v>7750000000</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="13">
         <v>43781</v>
       </c>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19">
+      <c r="M16" s="13"/>
+      <c r="N16" s="13">
         <v>43809</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="13">
         <v>43831</v>
       </c>
       <c r="P16" s="4">
@@ -15364,18 +15178,18 @@
       </c>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>66</v>
@@ -15387,7 +15201,7 @@
         <v>68</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="I17" s="4">
         <v>1027100000</v>
@@ -15398,14 +15212,14 @@
       <c r="K17" s="4">
         <v>1127675000</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="13">
         <v>43781</v>
       </c>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19">
+      <c r="M17" s="13"/>
+      <c r="N17" s="13">
         <v>43948</v>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="13">
         <v>44223</v>
       </c>
       <c r="P17" s="4">
@@ -15416,18 +15230,18 @@
       </c>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>66</v>
@@ -15439,7 +15253,7 @@
         <v>68</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I18" s="4">
         <v>9491491960</v>
@@ -15450,14 +15264,14 @@
       <c r="K18" s="4">
         <v>9935241960</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="13">
         <v>43781</v>
       </c>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19">
+      <c r="M18" s="13"/>
+      <c r="N18" s="13">
         <v>43872</v>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="13">
         <v>43979</v>
       </c>
       <c r="P18" s="4">
@@ -15468,18 +15282,18 @@
       </c>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>66</v>
@@ -15491,7 +15305,7 @@
         <v>68</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I19" s="4">
         <v>4024500000</v>
@@ -15502,14 +15316,14 @@
       <c r="K19" s="4">
         <v>4202000000</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="13">
         <v>43781</v>
       </c>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19">
+      <c r="M19" s="13"/>
+      <c r="N19" s="13">
         <v>43812</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="13">
         <v>43958</v>
       </c>
       <c r="P19" s="4">
@@ -15520,18 +15334,18 @@
       </c>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>66</v>
@@ -15543,7 +15357,7 @@
         <v>68</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I20" s="4">
         <v>20233937500</v>
@@ -15554,14 +15368,14 @@
       <c r="K20" s="4">
         <v>21162064500</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="13">
         <v>43781</v>
       </c>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19">
+      <c r="M20" s="13"/>
+      <c r="N20" s="13">
         <v>43902</v>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="13">
         <v>43943</v>
       </c>
       <c r="P20" s="4">
@@ -15572,18 +15386,18 @@
       </c>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>66</v>
@@ -15595,7 +15409,7 @@
         <v>68</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I21" s="4">
         <v>6524500000</v>
@@ -15606,14 +15420,14 @@
       <c r="K21" s="4">
         <v>6524500000</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="13">
         <v>43781</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19">
+      <c r="M21" s="13"/>
+      <c r="N21" s="13">
         <v>43969</v>
       </c>
-      <c r="O21" s="19">
+      <c r="O21" s="13">
         <v>43949</v>
       </c>
       <c r="P21" s="4">
@@ -15624,18 +15438,18 @@
       </c>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>66</v>
@@ -15647,7 +15461,7 @@
         <v>68</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I22" s="4">
         <v>2500000000</v>
@@ -15658,14 +15472,14 @@
       <c r="K22" s="4">
         <v>2588750000</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="13">
         <v>43812</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19">
+      <c r="M22" s="13"/>
+      <c r="N22" s="13">
         <v>43902</v>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="13">
         <v>43938</v>
       </c>
       <c r="P22" s="4">
@@ -15676,18 +15490,18 @@
       </c>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>66</v>
@@ -15699,7 +15513,7 @@
         <v>68</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I23" s="4">
         <v>3500000000</v>
@@ -15710,14 +15524,14 @@
       <c r="K23" s="4">
         <v>4154449000</v>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="13">
         <v>43812</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19">
+      <c r="M23" s="13"/>
+      <c r="N23" s="13">
         <v>43864</v>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="13">
         <v>44742</v>
       </c>
       <c r="P23" s="4">
@@ -15728,18 +15542,18 @@
       </c>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>66</v>
@@ -15751,7 +15565,7 @@
         <v>68</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I24" s="4">
         <v>3250000000</v>
@@ -15762,14 +15576,14 @@
       <c r="K24" s="4">
         <v>3477139308</v>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="13">
         <v>43798</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19">
+      <c r="M24" s="13"/>
+      <c r="N24" s="13">
         <v>43882</v>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="13">
         <v>43957</v>
       </c>
       <c r="P24" s="4">
@@ -15780,18 +15594,18 @@
       </c>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>66</v>
@@ -15803,7 +15617,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I25" s="4">
         <v>946000000</v>
@@ -15814,14 +15628,14 @@
       <c r="K25" s="4">
         <v>990375000</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="13">
         <v>43812</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19">
+      <c r="M25" s="13"/>
+      <c r="N25" s="13">
         <v>44043</v>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="13">
         <v>43991</v>
       </c>
       <c r="P25" s="4">
@@ -15832,18 +15646,18 @@
       </c>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>66</v>
@@ -15855,7 +15669,7 @@
         <v>68</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I26" s="4">
         <v>1943625000</v>
@@ -15866,14 +15680,14 @@
       <c r="K26" s="4">
         <v>2032375000</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="13">
         <v>43830</v>
       </c>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19">
+      <c r="M26" s="13"/>
+      <c r="N26" s="13">
         <v>44025</v>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="13">
         <v>44046</v>
       </c>
       <c r="P26" s="4">
@@ -15884,18 +15698,18 @@
       </c>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>66</v>
@@ -15907,7 +15721,7 @@
         <v>68</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I27" s="4">
         <v>1999999962.27</v>
@@ -15918,14 +15732,14 @@
       <c r="K27" s="4">
         <v>2667064893.9299998</v>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="13">
         <v>44111</v>
       </c>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19">
+      <c r="M27" s="13"/>
+      <c r="N27" s="13">
         <v>44319</v>
       </c>
-      <c r="O27" s="19">
+      <c r="O27" s="13">
         <v>44448</v>
       </c>
       <c r="P27" s="4">
@@ -15936,30 +15750,30 @@
       </c>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="22" t="s">
-        <v>453</v>
+      <c r="H28" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I28" s="4">
         <v>729826686</v>
@@ -15970,14 +15784,14 @@
       <c r="K28" s="4">
         <v>1195561547</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="13">
         <v>43825</v>
       </c>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19">
+      <c r="M28" s="13"/>
+      <c r="N28" s="13">
         <v>43875</v>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="13">
         <v>44074</v>
       </c>
       <c r="P28" s="4">
@@ -15988,30 +15802,30 @@
       </c>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>253</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H29" s="22" t="s">
-        <v>453</v>
+      <c r="H29" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I29" s="4">
         <v>37141732473</v>
@@ -16022,14 +15836,14 @@
       <c r="K29" s="4">
         <v>37141732473</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="13">
         <v>43812</v>
       </c>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19">
+      <c r="M29" s="13"/>
+      <c r="N29" s="13">
         <v>43817</v>
       </c>
-      <c r="O29" s="19">
+      <c r="O29" s="13">
         <v>44228</v>
       </c>
       <c r="P29" s="4">
@@ -16040,18 +15854,18 @@
       </c>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>92</v>
@@ -16062,8 +15876,8 @@
       <c r="G30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H30" s="23" t="s">
-        <v>462</v>
+      <c r="H30" s="16" t="s">
+        <v>451</v>
       </c>
       <c r="I30" s="4">
         <v>22507978719</v>
@@ -16074,14 +15888,14 @@
       <c r="K30" s="4">
         <v>22507978719</v>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="13">
         <v>44536</v>
       </c>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19">
+      <c r="M30" s="13"/>
+      <c r="N30" s="13">
         <v>44683</v>
       </c>
-      <c r="O30" s="19">
+      <c r="O30" s="13">
         <v>44837</v>
       </c>
       <c r="P30" s="4">
@@ -16092,30 +15906,30 @@
       </c>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I31" s="4">
         <v>38700180208.470001</v>
@@ -16126,14 +15940,14 @@
       <c r="K31" s="4">
         <v>38936180208.470001</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="13">
         <v>44195</v>
       </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19">
+      <c r="M31" s="13"/>
+      <c r="N31" s="13">
         <v>44952</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="13">
         <v>44595</v>
       </c>
       <c r="P31" s="4">
@@ -16144,18 +15958,18 @@
       </c>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>92</v>
@@ -16166,8 +15980,8 @@
       <c r="G32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="22" t="s">
-        <v>453</v>
+      <c r="H32" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I32" s="4">
         <v>75409582200</v>
@@ -16178,14 +15992,14 @@
       <c r="K32" s="4">
         <v>75409582200</v>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="13">
         <v>44195</v>
       </c>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19">
+      <c r="M32" s="13"/>
+      <c r="N32" s="13">
         <v>44326</v>
       </c>
-      <c r="O32" s="19">
+      <c r="O32" s="13">
         <v>44445</v>
       </c>
       <c r="P32" s="4">
@@ -16196,18 +16010,18 @@
       </c>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>66</v>
@@ -16219,7 +16033,7 @@
         <v>57</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I33" s="4">
         <v>1998000000</v>
@@ -16230,14 +16044,14 @@
       <c r="K33" s="4">
         <v>2414100000</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="13">
         <v>43950</v>
       </c>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19">
+      <c r="M33" s="13"/>
+      <c r="N33" s="13">
         <v>44001</v>
       </c>
-      <c r="O33" s="19">
+      <c r="O33" s="13">
         <v>44133</v>
       </c>
       <c r="P33" s="4">
@@ -16248,18 +16062,18 @@
       </c>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>66</v>
@@ -16271,7 +16085,7 @@
         <v>57</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I34" s="4">
         <v>1999306318</v>
@@ -16282,14 +16096,14 @@
       <c r="K34" s="4">
         <v>3490315624.7199998</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="13">
         <v>43924</v>
       </c>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19">
+      <c r="M34" s="13"/>
+      <c r="N34" s="13">
         <v>44001</v>
       </c>
-      <c r="O34" s="19">
+      <c r="O34" s="13">
         <v>44118</v>
       </c>
       <c r="P34" s="4">
@@ -16300,18 +16114,18 @@
       </c>
       <c r="R34" s="3"/>
     </row>
-    <row r="35" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>66</v>
@@ -16323,7 +16137,7 @@
         <v>207</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I35" s="4">
         <v>1999910691</v>
@@ -16334,14 +16148,14 @@
       <c r="K35" s="4">
         <v>3839181953</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="13">
         <v>44078</v>
       </c>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19">
+      <c r="M35" s="13"/>
+      <c r="N35" s="13">
         <v>45385</v>
       </c>
-      <c r="O35" s="19">
+      <c r="O35" s="13">
         <v>44252</v>
       </c>
       <c r="P35" s="4">
@@ -16352,18 +16166,18 @@
       </c>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>66</v>
@@ -16375,7 +16189,7 @@
         <v>68</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I36" s="4">
         <v>1999433630</v>
@@ -16386,14 +16200,14 @@
       <c r="K36" s="4">
         <v>2930484800</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="13">
         <v>43924</v>
       </c>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19">
+      <c r="M36" s="13"/>
+      <c r="N36" s="13">
         <v>44106</v>
       </c>
-      <c r="O36" s="19">
+      <c r="O36" s="13">
         <v>44106</v>
       </c>
       <c r="P36" s="4">
@@ -16404,18 +16218,18 @@
       </c>
       <c r="R36" s="3"/>
     </row>
-    <row r="37" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>66</v>
@@ -16427,7 +16241,7 @@
         <v>68</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I37" s="4">
         <v>1999976897</v>
@@ -16438,14 +16252,14 @@
       <c r="K37" s="4">
         <v>2612747413</v>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="13">
         <v>44078</v>
       </c>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19">
+      <c r="M37" s="13"/>
+      <c r="N37" s="13">
         <v>44179</v>
       </c>
-      <c r="O37" s="19">
+      <c r="O37" s="13">
         <v>44229</v>
       </c>
       <c r="P37" s="4">
@@ -16456,18 +16270,18 @@
       </c>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>66</v>
@@ -16479,7 +16293,7 @@
         <v>57</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I38" s="4">
         <v>1272365336</v>
@@ -16490,14 +16304,12 @@
       <c r="K38" s="4">
         <v>1915671336</v>
       </c>
-      <c r="L38" s="19">
+      <c r="L38" s="13">
         <v>44078</v>
       </c>
-      <c r="M38" s="19"/>
-      <c r="N38" s="20" t="s">
-        <v>904</v>
-      </c>
-      <c r="O38" s="19">
+      <c r="M38" s="13"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="13">
         <v>44421</v>
       </c>
       <c r="P38" s="4">
@@ -16508,18 +16320,18 @@
       </c>
       <c r="R38" s="3"/>
     </row>
-    <row r="39" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>66</v>
@@ -16531,7 +16343,7 @@
         <v>68</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I39" s="4">
         <v>1999833255</v>
@@ -16542,14 +16354,14 @@
       <c r="K39" s="4">
         <v>2948047175</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="13">
         <v>44078</v>
       </c>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19">
+      <c r="M39" s="13"/>
+      <c r="N39" s="13">
         <v>44113</v>
       </c>
-      <c r="O39" s="19">
+      <c r="O39" s="13">
         <v>44408</v>
       </c>
       <c r="P39" s="4">
@@ -16560,18 +16372,18 @@
       </c>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>66</v>
@@ -16583,7 +16395,7 @@
         <v>57</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I40" s="4">
         <v>6559568533</v>
@@ -16594,14 +16406,14 @@
       <c r="K40" s="4">
         <v>6848145520</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="13">
         <v>44159</v>
       </c>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19">
+      <c r="M40" s="13"/>
+      <c r="N40" s="13">
         <v>44337</v>
       </c>
-      <c r="O40" s="19">
+      <c r="O40" s="13">
         <v>44410</v>
       </c>
       <c r="P40" s="4">
@@ -16612,18 +16424,18 @@
       </c>
       <c r="R40" s="3"/>
     </row>
-    <row r="41" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>66</v>
@@ -16635,7 +16447,7 @@
         <v>68</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="I41" s="4">
         <v>1998890586.73</v>
@@ -16646,14 +16458,14 @@
       <c r="K41" s="4">
         <v>2898886012.6100001</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="13">
         <v>44078</v>
       </c>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19">
+      <c r="M41" s="13"/>
+      <c r="N41" s="13">
         <v>44386</v>
       </c>
-      <c r="O41" s="19">
+      <c r="O41" s="13">
         <v>44335</v>
       </c>
       <c r="P41" s="4">
@@ -16664,18 +16476,18 @@
       </c>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>66</v>
@@ -16687,7 +16499,7 @@
         <v>207</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I42" s="4">
         <v>5347795060</v>
@@ -16698,14 +16510,14 @@
       <c r="K42" s="4">
         <v>6581633763</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="13">
         <v>43966</v>
       </c>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19">
+      <c r="M42" s="13"/>
+      <c r="N42" s="13">
         <v>43978</v>
       </c>
-      <c r="O42" s="19">
+      <c r="O42" s="13">
         <v>44097</v>
       </c>
       <c r="P42" s="4">
@@ -16716,18 +16528,18 @@
       </c>
       <c r="R42" s="3"/>
     </row>
-    <row r="43" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>670</v>
+    <row r="43" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
+        <v>658</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>66</v>
@@ -16739,7 +16551,7 @@
         <v>68</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I43" s="4">
         <v>1965295196.9400001</v>
@@ -16750,12 +16562,12 @@
       <c r="K43" s="4">
         <v>4131804023.6700001</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="13">
         <v>44078</v>
       </c>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19">
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13">
         <v>44421</v>
       </c>
       <c r="P43" s="4">
@@ -16766,18 +16578,18 @@
       </c>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>66</v>
@@ -16789,7 +16601,7 @@
         <v>68</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I44" s="4">
         <v>8764697664</v>
@@ -16800,14 +16612,14 @@
       <c r="K44" s="4">
         <v>10308364564</v>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="13">
         <v>44432</v>
       </c>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19">
+      <c r="M44" s="13"/>
+      <c r="N44" s="13">
         <v>44480</v>
       </c>
-      <c r="O44" s="19">
+      <c r="O44" s="13">
         <v>44502</v>
       </c>
       <c r="P44" s="4">
@@ -16818,18 +16630,18 @@
       </c>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>66</v>
@@ -16841,7 +16653,7 @@
         <v>57</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I45" s="4">
         <v>1349000868</v>
@@ -16852,14 +16664,14 @@
       <c r="K45" s="4">
         <v>1409240868</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="13">
         <v>44111</v>
       </c>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19">
+      <c r="M45" s="13"/>
+      <c r="N45" s="13">
         <v>44568</v>
       </c>
-      <c r="O45" s="19">
+      <c r="O45" s="13">
         <v>44594</v>
       </c>
       <c r="P45" s="4">
@@ -16870,18 +16682,18 @@
       </c>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>66</v>
@@ -16893,7 +16705,7 @@
         <v>57</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I46" s="4">
         <v>3106000000</v>
@@ -16904,14 +16716,14 @@
       <c r="K46" s="4">
         <v>3156000000</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="13">
         <v>44159</v>
       </c>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19">
+      <c r="M46" s="13"/>
+      <c r="N46" s="13">
         <v>44235</v>
       </c>
-      <c r="O46" s="19">
+      <c r="O46" s="13">
         <v>44327</v>
       </c>
       <c r="P46" s="4">
@@ -16922,18 +16734,18 @@
       </c>
       <c r="R46" s="3"/>
     </row>
-    <row r="47" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>66</v>
@@ -16945,7 +16757,7 @@
         <v>57</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="I47" s="4">
         <v>8995267958.5699997</v>
@@ -16956,14 +16768,14 @@
       <c r="K47" s="4">
         <v>9177414454.0599995</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="13">
         <v>44159</v>
       </c>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19">
+      <c r="M47" s="13"/>
+      <c r="N47" s="13">
         <v>44263</v>
       </c>
-      <c r="O47" s="19">
+      <c r="O47" s="13">
         <v>44365</v>
       </c>
       <c r="P47" s="4">
@@ -16974,18 +16786,18 @@
       </c>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>66</v>
@@ -16997,7 +16809,7 @@
         <v>68</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I48" s="4">
         <v>6750000000</v>
@@ -17008,14 +16820,14 @@
       <c r="K48" s="4">
         <v>6920233499</v>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="13">
         <v>44330</v>
       </c>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19">
+      <c r="M48" s="13"/>
+      <c r="N48" s="13">
         <v>44362</v>
       </c>
-      <c r="O48" s="19">
+      <c r="O48" s="13">
         <v>44404</v>
       </c>
       <c r="P48" s="4">
@@ -17026,18 +16838,18 @@
       </c>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>66</v>
@@ -17049,7 +16861,7 @@
         <v>68</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I49" s="4">
         <v>1998157618.8800001</v>
@@ -17060,14 +16872,14 @@
       <c r="K49" s="4">
         <v>2467892722.71</v>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="13">
         <v>44159</v>
       </c>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19">
+      <c r="M49" s="13"/>
+      <c r="N49" s="13">
         <v>44259</v>
       </c>
-      <c r="O49" s="19">
+      <c r="O49" s="13">
         <v>44567</v>
       </c>
       <c r="P49" s="4">
@@ -17078,18 +16890,18 @@
       </c>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>66</v>
@@ -17101,7 +16913,7 @@
         <v>68</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I50" s="4">
         <v>2000000000</v>
@@ -17112,14 +16924,14 @@
       <c r="K50" s="4">
         <v>2474185221</v>
       </c>
-      <c r="L50" s="19">
+      <c r="L50" s="13">
         <v>44159</v>
       </c>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19">
+      <c r="M50" s="13"/>
+      <c r="N50" s="13">
         <v>44246</v>
       </c>
-      <c r="O50" s="19">
+      <c r="O50" s="13">
         <v>44337</v>
       </c>
       <c r="P50" s="4">
@@ -17130,18 +16942,18 @@
       </c>
       <c r="R50" s="3"/>
     </row>
-    <row r="51" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>66</v>
@@ -17153,7 +16965,7 @@
         <v>68</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I51" s="4">
         <v>5335769261</v>
@@ -17164,14 +16976,12 @@
       <c r="K51" s="4">
         <v>5913070114</v>
       </c>
-      <c r="L51" s="19">
+      <c r="L51" s="13">
         <v>44348</v>
       </c>
-      <c r="M51" s="19"/>
-      <c r="N51" s="20" t="s">
-        <v>904</v>
-      </c>
-      <c r="O51" s="19">
+      <c r="M51" s="13"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="13">
         <v>44427</v>
       </c>
       <c r="P51" s="4">
@@ -17182,18 +16992,18 @@
       </c>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>66</v>
@@ -17205,7 +17015,7 @@
         <v>68</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I52" s="4">
         <v>4940449374</v>
@@ -17216,14 +17026,14 @@
       <c r="K52" s="4">
         <v>5203930460</v>
       </c>
-      <c r="L52" s="19">
+      <c r="L52" s="13">
         <v>44432</v>
       </c>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19">
+      <c r="M52" s="13"/>
+      <c r="N52" s="13">
         <v>44480</v>
       </c>
-      <c r="O52" s="19">
+      <c r="O52" s="13">
         <v>44517</v>
       </c>
       <c r="P52" s="4">
@@ -17234,18 +17044,18 @@
       </c>
       <c r="R52" s="3"/>
     </row>
-    <row r="53" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>66</v>
@@ -17257,7 +17067,7 @@
         <v>57</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="I53" s="4">
         <v>1999924866</v>
@@ -17268,14 +17078,14 @@
       <c r="K53" s="4">
         <v>3559208215</v>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="13">
         <v>44159</v>
       </c>
-      <c r="M53" s="19"/>
-      <c r="N53" s="19">
+      <c r="M53" s="13"/>
+      <c r="N53" s="13">
         <v>44246</v>
       </c>
-      <c r="O53" s="19">
+      <c r="O53" s="13">
         <v>44341</v>
       </c>
       <c r="P53" s="4">
@@ -17286,18 +17096,18 @@
       </c>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>66</v>
@@ -17309,7 +17119,7 @@
         <v>68</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I54" s="4">
         <v>3591118773</v>
@@ -17320,14 +17130,14 @@
       <c r="K54" s="4">
         <v>3768618773</v>
       </c>
-      <c r="L54" s="19">
+      <c r="L54" s="13">
         <v>44330</v>
       </c>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19">
+      <c r="M54" s="13"/>
+      <c r="N54" s="13">
         <v>44393</v>
       </c>
-      <c r="O54" s="19">
+      <c r="O54" s="13">
         <v>44418</v>
       </c>
       <c r="P54" s="4">
@@ -17338,18 +17148,18 @@
       </c>
       <c r="R54" s="3"/>
     </row>
-    <row r="55" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>66</v>
@@ -17361,7 +17171,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I55" s="4">
         <v>2000000000</v>
@@ -17372,14 +17182,14 @@
       <c r="K55" s="4">
         <v>3560969376</v>
       </c>
-      <c r="L55" s="19">
+      <c r="L55" s="13">
         <v>44159</v>
       </c>
-      <c r="M55" s="19"/>
-      <c r="N55" s="19">
+      <c r="M55" s="13"/>
+      <c r="N55" s="13">
         <v>44246</v>
       </c>
-      <c r="O55" s="19">
+      <c r="O55" s="13">
         <v>44337</v>
       </c>
       <c r="P55" s="4">
@@ -17390,18 +17200,18 @@
       </c>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>66</v>
@@ -17413,7 +17223,7 @@
         <v>68</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I56" s="4">
         <v>1999112638.9200001</v>
@@ -17424,14 +17234,14 @@
       <c r="K56" s="4">
         <v>2856350066.9200001</v>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="13">
         <v>44159</v>
       </c>
-      <c r="M56" s="19"/>
-      <c r="N56" s="19">
+      <c r="M56" s="13"/>
+      <c r="N56" s="13">
         <v>44259</v>
       </c>
-      <c r="O56" s="19">
+      <c r="O56" s="13">
         <v>44474</v>
       </c>
       <c r="P56" s="4">
@@ -17442,18 +17252,18 @@
       </c>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>66</v>
@@ -17465,7 +17275,7 @@
         <v>68</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I57" s="4">
         <v>7500000000</v>
@@ -17476,14 +17286,14 @@
       <c r="K57" s="4">
         <v>7500000000</v>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="13">
         <v>44348</v>
       </c>
-      <c r="M57" s="19"/>
-      <c r="N57" s="19">
+      <c r="M57" s="13"/>
+      <c r="N57" s="13">
         <v>44379</v>
       </c>
-      <c r="O57" s="19">
+      <c r="O57" s="13">
         <v>44407</v>
       </c>
       <c r="P57" s="4">
@@ -17494,18 +17304,18 @@
       </c>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>66</v>
@@ -17517,7 +17327,7 @@
         <v>57</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I58" s="4">
         <v>1999803848</v>
@@ -17528,14 +17338,14 @@
       <c r="K58" s="4">
         <v>3394230296</v>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="13">
         <v>44159</v>
       </c>
-      <c r="M58" s="19"/>
-      <c r="N58" s="19">
+      <c r="M58" s="13"/>
+      <c r="N58" s="13">
         <v>44320</v>
       </c>
-      <c r="O58" s="19">
+      <c r="O58" s="13">
         <v>44467</v>
       </c>
       <c r="P58" s="4">
@@ -17546,18 +17356,18 @@
       </c>
       <c r="R58" s="3"/>
     </row>
-    <row r="59" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>66</v>
@@ -17569,7 +17379,7 @@
         <v>68</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="I59" s="4">
         <v>1738785560</v>
@@ -17580,14 +17390,14 @@
       <c r="K59" s="4">
         <v>2346358031</v>
       </c>
-      <c r="L59" s="19">
+      <c r="L59" s="13">
         <v>44159</v>
       </c>
-      <c r="M59" s="19"/>
-      <c r="N59" s="19">
+      <c r="M59" s="13"/>
+      <c r="N59" s="13">
         <v>44309</v>
       </c>
-      <c r="O59" s="19">
+      <c r="O59" s="13">
         <v>44337</v>
       </c>
       <c r="P59" s="4">
@@ -17598,18 +17408,18 @@
       </c>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>66</v>
@@ -17621,7 +17431,7 @@
         <v>57</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I60" s="4">
         <v>1999000000</v>
@@ -17632,14 +17442,14 @@
       <c r="K60" s="4">
         <v>2511000000</v>
       </c>
-      <c r="L60" s="19">
+      <c r="L60" s="13">
         <v>44159</v>
       </c>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19">
+      <c r="M60" s="13"/>
+      <c r="N60" s="13">
         <v>44246</v>
       </c>
-      <c r="O60" s="19">
+      <c r="O60" s="13">
         <v>44340</v>
       </c>
       <c r="P60" s="4">
@@ -17650,18 +17460,18 @@
       </c>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>66</v>
@@ -17673,7 +17483,7 @@
         <v>68</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I61" s="4">
         <v>1775630700</v>
@@ -17684,14 +17494,14 @@
       <c r="K61" s="4">
         <v>1894532100</v>
       </c>
-      <c r="L61" s="19">
+      <c r="L61" s="13">
         <v>44368</v>
       </c>
-      <c r="M61" s="19"/>
-      <c r="N61" s="19">
+      <c r="M61" s="13"/>
+      <c r="N61" s="13">
         <v>44924</v>
       </c>
-      <c r="O61" s="19">
+      <c r="O61" s="13">
         <v>44456</v>
       </c>
       <c r="P61" s="4">
@@ -17702,18 +17512,18 @@
       </c>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>66</v>
@@ -17725,7 +17535,7 @@
         <v>68</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I62" s="4">
         <v>750000000</v>
@@ -17736,14 +17546,14 @@
       <c r="K62" s="4">
         <v>918904760</v>
       </c>
-      <c r="L62" s="19">
+      <c r="L62" s="13">
         <v>44377</v>
       </c>
-      <c r="M62" s="19"/>
-      <c r="N62" s="19">
+      <c r="M62" s="13"/>
+      <c r="N62" s="13">
         <v>44440</v>
       </c>
-      <c r="O62" s="19">
+      <c r="O62" s="13">
         <v>44589</v>
       </c>
       <c r="P62" s="4">
@@ -17754,18 +17564,18 @@
       </c>
       <c r="R62" s="3"/>
     </row>
-    <row r="63" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>66</v>
@@ -17777,7 +17587,7 @@
         <v>68</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I63" s="4">
         <v>2828005287</v>
@@ -17788,14 +17598,14 @@
       <c r="K63" s="4">
         <v>3069617150</v>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="13">
         <v>44348</v>
       </c>
-      <c r="M63" s="19"/>
-      <c r="N63" s="19">
+      <c r="M63" s="13"/>
+      <c r="N63" s="13">
         <v>44924</v>
       </c>
-      <c r="O63" s="19">
+      <c r="O63" s="13">
         <v>44410</v>
       </c>
       <c r="P63" s="4">
@@ -17806,30 +17616,30 @@
       </c>
       <c r="R63" s="3"/>
     </row>
-    <row r="64" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H64" s="22" t="s">
-        <v>467</v>
+      <c r="H64" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I64" s="4">
         <v>69047758069</v>
@@ -17840,14 +17650,14 @@
       <c r="K64" s="4">
         <v>69047758069</v>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="13">
         <v>44551</v>
       </c>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19">
+      <c r="M64" s="13"/>
+      <c r="N64" s="13">
         <v>44652</v>
       </c>
-      <c r="O64" s="19">
+      <c r="O64" s="13">
         <v>44810</v>
       </c>
       <c r="P64" s="4">
@@ -17858,18 +17668,18 @@
       </c>
       <c r="R64" s="3"/>
     </row>
-    <row r="65" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>66</v>
@@ -17881,7 +17691,7 @@
         <v>68</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I65" s="4">
         <v>17635937500</v>
@@ -17892,14 +17702,14 @@
       <c r="K65" s="4">
         <v>18418143500</v>
       </c>
-      <c r="L65" s="19">
+      <c r="L65" s="13">
         <v>44330</v>
       </c>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19">
+      <c r="M65" s="13"/>
+      <c r="N65" s="13">
         <v>44365</v>
       </c>
-      <c r="O65" s="19">
+      <c r="O65" s="13">
         <v>44438</v>
       </c>
       <c r="P65" s="4">
@@ -17910,18 +17720,18 @@
       </c>
       <c r="R65" s="3"/>
     </row>
-    <row r="66" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>66</v>
@@ -17933,7 +17743,7 @@
         <v>68</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I66" s="4">
         <v>1309600000</v>
@@ -17944,14 +17754,14 @@
       <c r="K66" s="4">
         <v>1519950000</v>
       </c>
-      <c r="L66" s="19">
+      <c r="L66" s="13">
         <v>44348</v>
       </c>
-      <c r="M66" s="19"/>
-      <c r="N66" s="19">
+      <c r="M66" s="13"/>
+      <c r="N66" s="13">
         <v>44924</v>
       </c>
-      <c r="O66" s="19">
+      <c r="O66" s="13">
         <v>44466</v>
       </c>
       <c r="P66" s="4">
@@ -17962,18 +17772,18 @@
       </c>
       <c r="R66" s="3"/>
     </row>
-    <row r="67" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>66</v>
@@ -17985,7 +17795,7 @@
         <v>68</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I67" s="4">
         <v>2750000000</v>
@@ -17996,14 +17806,14 @@
       <c r="K67" s="4">
         <v>2775000000</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="13">
         <v>44384</v>
       </c>
-      <c r="M67" s="19"/>
-      <c r="N67" s="19">
+      <c r="M67" s="13"/>
+      <c r="N67" s="13">
         <v>44429</v>
       </c>
-      <c r="O67" s="19">
+      <c r="O67" s="13">
         <v>44530</v>
       </c>
       <c r="P67" s="4">
@@ -18014,18 +17824,18 @@
       </c>
       <c r="R67" s="3"/>
     </row>
-    <row r="68" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>66</v>
@@ -18037,7 +17847,7 @@
         <v>68</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I68" s="4">
         <v>1500000000</v>
@@ -18048,14 +17858,14 @@
       <c r="K68" s="4">
         <v>1853734000</v>
       </c>
-      <c r="L68" s="19">
+      <c r="L68" s="13">
         <v>44368</v>
       </c>
-      <c r="M68" s="19"/>
-      <c r="N68" s="19">
+      <c r="M68" s="13"/>
+      <c r="N68" s="13">
         <v>44368</v>
       </c>
-      <c r="O68" s="19">
+      <c r="O68" s="13">
         <v>44433</v>
       </c>
       <c r="P68" s="4">
@@ -18066,18 +17876,18 @@
       </c>
       <c r="R68" s="3"/>
     </row>
-    <row r="69" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>66</v>
@@ -18089,7 +17899,7 @@
         <v>68</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I69" s="4">
         <v>1411798728</v>
@@ -18100,14 +17910,14 @@
       <c r="K69" s="4">
         <v>1532348536</v>
       </c>
-      <c r="L69" s="19">
+      <c r="L69" s="13">
         <v>44368</v>
       </c>
-      <c r="M69" s="19"/>
-      <c r="N69" s="19">
+      <c r="M69" s="13"/>
+      <c r="N69" s="13">
         <v>44925</v>
       </c>
-      <c r="O69" s="19">
+      <c r="O69" s="13">
         <v>44407</v>
       </c>
       <c r="P69" s="4">
@@ -18118,18 +17928,18 @@
       </c>
       <c r="R69" s="3"/>
     </row>
-    <row r="70" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>66</v>
@@ -18141,7 +17951,7 @@
         <v>68</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I70" s="4">
         <v>1999997728</v>
@@ -18152,14 +17962,14 @@
       <c r="K70" s="4">
         <v>2663232448</v>
       </c>
-      <c r="L70" s="19">
+      <c r="L70" s="13">
         <v>44536</v>
       </c>
-      <c r="M70" s="19"/>
-      <c r="N70" s="19">
+      <c r="M70" s="13"/>
+      <c r="N70" s="13">
         <v>44533</v>
       </c>
-      <c r="O70" s="19">
+      <c r="O70" s="13">
         <v>44713</v>
       </c>
       <c r="P70" s="4">
@@ -18170,18 +17980,18 @@
       </c>
       <c r="R70" s="3"/>
     </row>
-    <row r="71" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>66</v>
@@ -18193,7 +18003,7 @@
         <v>68</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I71" s="4">
         <v>1999667231.96</v>
@@ -18204,14 +18014,14 @@
       <c r="K71" s="4">
         <v>3035821023.1599998</v>
       </c>
-      <c r="L71" s="19">
+      <c r="L71" s="13">
         <v>44537</v>
       </c>
-      <c r="M71" s="19"/>
-      <c r="N71" s="19">
+      <c r="M71" s="13"/>
+      <c r="N71" s="13">
         <v>44606</v>
       </c>
-      <c r="O71" s="19">
+      <c r="O71" s="13">
         <v>44721</v>
       </c>
       <c r="P71" s="4">
@@ -18222,18 +18032,18 @@
       </c>
       <c r="R71" s="3"/>
     </row>
-    <row r="72" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>66</v>
@@ -18245,7 +18055,7 @@
         <v>207</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="I72" s="4">
         <v>2000000000</v>
@@ -18256,14 +18066,14 @@
       <c r="K72" s="4">
         <v>2896725569</v>
       </c>
-      <c r="L72" s="19">
+      <c r="L72" s="13">
         <v>44537</v>
       </c>
-      <c r="M72" s="19"/>
-      <c r="N72" s="19">
+      <c r="M72" s="13"/>
+      <c r="N72" s="13">
         <v>44606</v>
       </c>
-      <c r="O72" s="19">
+      <c r="O72" s="13">
         <v>44740</v>
       </c>
       <c r="P72" s="4">
@@ -18274,18 +18084,18 @@
       </c>
       <c r="R72" s="3"/>
     </row>
-    <row r="73" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>66</v>
@@ -18297,7 +18107,7 @@
         <v>68</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I73" s="4">
         <v>1953855779</v>
@@ -18308,14 +18118,14 @@
       <c r="K73" s="4">
         <v>2459776116</v>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="13">
         <v>44537</v>
       </c>
-      <c r="M73" s="19"/>
-      <c r="N73" s="19">
+      <c r="M73" s="13"/>
+      <c r="N73" s="13">
         <v>44606</v>
       </c>
-      <c r="O73" s="19">
+      <c r="O73" s="13">
         <v>44713</v>
       </c>
       <c r="P73" s="4">
@@ -18326,18 +18136,18 @@
       </c>
       <c r="R73" s="3"/>
     </row>
-    <row r="74" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>66</v>
@@ -18349,7 +18159,7 @@
         <v>57</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I74" s="4">
         <v>4351936180</v>
@@ -18360,14 +18170,14 @@
       <c r="K74" s="4">
         <v>4451936180</v>
       </c>
-      <c r="L74" s="19">
+      <c r="L74" s="13">
         <v>44552</v>
       </c>
-      <c r="M74" s="19"/>
-      <c r="N74" s="19">
+      <c r="M74" s="13"/>
+      <c r="N74" s="13">
         <v>44560</v>
       </c>
-      <c r="O74" s="19">
+      <c r="O74" s="13">
         <v>44588</v>
       </c>
       <c r="P74" s="4">
@@ -18378,18 +18188,18 @@
       </c>
       <c r="R74" s="3"/>
     </row>
-    <row r="75" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>66</v>
@@ -18401,7 +18211,7 @@
         <v>57</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I75" s="4">
         <v>19906880779</v>
@@ -18412,14 +18222,14 @@
       <c r="K75" s="4">
         <v>19978880779</v>
       </c>
-      <c r="L75" s="19">
+      <c r="L75" s="13">
         <v>44700</v>
       </c>
-      <c r="M75" s="19"/>
-      <c r="N75" s="19">
+      <c r="M75" s="13"/>
+      <c r="N75" s="13">
         <v>44756</v>
       </c>
-      <c r="O75" s="19">
+      <c r="O75" s="13">
         <v>44783</v>
       </c>
       <c r="P75" s="4">
@@ -18430,18 +18240,18 @@
       </c>
       <c r="R75" s="3"/>
     </row>
-    <row r="76" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>253</v>
@@ -18452,8 +18262,8 @@
       <c r="G76" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H76" s="22" t="s">
-        <v>453</v>
+      <c r="H76" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I76" s="4">
         <v>3981132848.27</v>
@@ -18464,14 +18274,14 @@
       <c r="K76" s="4">
         <v>3981132848.27</v>
       </c>
-      <c r="L76" s="19">
+      <c r="L76" s="13">
         <v>44509</v>
       </c>
-      <c r="M76" s="19"/>
-      <c r="N76" s="19">
+      <c r="M76" s="13"/>
+      <c r="N76" s="13">
         <v>44511</v>
       </c>
-      <c r="O76" s="19">
+      <c r="O76" s="13">
         <v>44594</v>
       </c>
       <c r="P76" s="4">
@@ -18482,28 +18292,28 @@
       </c>
       <c r="R76" s="3"/>
     </row>
-    <row r="77" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="21" t="s">
-        <v>782</v>
+    <row r="77" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="14" t="s">
+        <v>770</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H77" s="24" t="s">
-        <v>507</v>
+      <c r="H77" s="17" t="s">
+        <v>496</v>
       </c>
       <c r="I77" s="4">
         <v>2407058486</v>
@@ -18514,12 +18324,12 @@
       <c r="K77" s="4">
         <v>2407275254.8200002</v>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="13">
         <v>44844</v>
       </c>
-      <c r="M77" s="19"/>
-      <c r="N77" s="19"/>
-      <c r="O77" s="19"/>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13"/>
       <c r="P77" s="4">
         <v>0</v>
       </c>
@@ -18528,30 +18338,30 @@
       </c>
       <c r="R77" s="3"/>
     </row>
-    <row r="78" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H78" s="22" t="s">
-        <v>462</v>
+      <c r="H78" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I78" s="4">
         <v>45601872749</v>
@@ -18562,14 +18372,14 @@
       <c r="K78" s="4">
         <v>45601872749</v>
       </c>
-      <c r="L78" s="19">
+      <c r="L78" s="13">
         <v>44560</v>
       </c>
-      <c r="M78" s="19"/>
-      <c r="N78" s="19">
+      <c r="M78" s="13"/>
+      <c r="N78" s="13">
         <v>44559</v>
       </c>
-      <c r="O78" s="19">
+      <c r="O78" s="13">
         <v>44669</v>
       </c>
       <c r="P78" s="4">
@@ -18580,18 +18390,18 @@
       </c>
       <c r="R78" s="3"/>
     </row>
-    <row r="79" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>92</v>
@@ -18602,8 +18412,8 @@
       <c r="G79" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H79" s="22" t="s">
-        <v>462</v>
+      <c r="H79" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I79" s="4">
         <v>2489078661</v>
@@ -18614,14 +18424,14 @@
       <c r="K79" s="4">
         <v>2489078661</v>
       </c>
-      <c r="L79" s="19">
+      <c r="L79" s="13">
         <v>44559</v>
       </c>
-      <c r="M79" s="19"/>
-      <c r="N79" s="19" t="s">
-        <v>905</v>
-      </c>
-      <c r="O79" s="19">
+      <c r="M79" s="13"/>
+      <c r="N79" s="13">
+        <v>44559</v>
+      </c>
+      <c r="O79" s="13">
         <v>44810</v>
       </c>
       <c r="P79" s="4">
@@ -18632,18 +18442,18 @@
       </c>
       <c r="R79" s="3"/>
     </row>
-    <row r="80" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>92</v>
@@ -18654,8 +18464,8 @@
       <c r="G80" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H80" s="22" t="s">
-        <v>467</v>
+      <c r="H80" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I80" s="4">
         <v>18036167387.900002</v>
@@ -18666,14 +18476,12 @@
       <c r="K80" s="4">
         <v>18036167387.900002</v>
       </c>
-      <c r="L80" s="19">
+      <c r="L80" s="13">
         <v>44559</v>
       </c>
-      <c r="M80" s="19"/>
-      <c r="N80" s="19" t="s">
-        <v>904</v>
-      </c>
-      <c r="O80" s="19">
+      <c r="M80" s="13"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="13">
         <v>44708</v>
       </c>
       <c r="P80" s="4">
@@ -18684,18 +18492,18 @@
       </c>
       <c r="R80" s="3"/>
     </row>
-    <row r="81" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>92</v>
@@ -18706,8 +18514,8 @@
       <c r="G81" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H81" s="23" t="s">
-        <v>467</v>
+      <c r="H81" s="16" t="s">
+        <v>456</v>
       </c>
       <c r="I81" s="4">
         <v>41816156185</v>
@@ -18718,14 +18526,14 @@
       <c r="K81" s="4">
         <v>41816156185</v>
       </c>
-      <c r="L81" s="19">
+      <c r="L81" s="13">
         <v>44624</v>
       </c>
-      <c r="M81" s="19"/>
-      <c r="N81" s="19">
+      <c r="M81" s="13"/>
+      <c r="N81" s="13">
         <v>44624</v>
       </c>
-      <c r="O81" s="19">
+      <c r="O81" s="13">
         <v>44873</v>
       </c>
       <c r="P81" s="4">
@@ -18736,18 +18544,18 @@
       </c>
       <c r="R81" s="3"/>
     </row>
-    <row r="82" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>66</v>
@@ -18759,7 +18567,7 @@
         <v>68</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I82" s="4">
         <v>9606506835</v>
@@ -18770,14 +18578,14 @@
       <c r="K82" s="4">
         <v>9696506835</v>
       </c>
-      <c r="L82" s="19">
+      <c r="L82" s="13">
         <v>44887</v>
       </c>
-      <c r="M82" s="19"/>
-      <c r="N82" s="19">
+      <c r="M82" s="13"/>
+      <c r="N82" s="13">
         <v>44911</v>
       </c>
-      <c r="O82" s="19">
+      <c r="O82" s="13">
         <v>45070</v>
       </c>
       <c r="P82" s="4">
@@ -18788,18 +18596,18 @@
       </c>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>66</v>
@@ -18811,7 +18619,7 @@
         <v>57</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I83" s="4">
         <v>500000000</v>
@@ -18822,14 +18630,14 @@
       <c r="K83" s="4">
         <v>585470000</v>
       </c>
-      <c r="L83" s="19">
+      <c r="L83" s="13">
         <v>44887</v>
       </c>
-      <c r="M83" s="19"/>
-      <c r="N83" s="19">
+      <c r="M83" s="13"/>
+      <c r="N83" s="13">
         <v>44930</v>
       </c>
-      <c r="O83" s="19">
+      <c r="O83" s="13">
         <v>44986</v>
       </c>
       <c r="P83" s="4">
@@ -18840,18 +18648,18 @@
       </c>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>66</v>
@@ -18863,7 +18671,7 @@
         <v>68</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I84" s="4">
         <v>4299593384</v>
@@ -18874,14 +18682,14 @@
       <c r="K84" s="4">
         <v>4425738451</v>
       </c>
-      <c r="L84" s="19">
+      <c r="L84" s="13">
         <v>44914</v>
       </c>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19">
+      <c r="M84" s="13"/>
+      <c r="N84" s="13">
         <v>45055</v>
       </c>
-      <c r="O84" s="19">
+      <c r="O84" s="13">
         <v>45139</v>
       </c>
       <c r="P84" s="4">
@@ -18892,18 +18700,18 @@
       </c>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>198</v>
@@ -18914,8 +18722,8 @@
       <c r="G85" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H85" s="22" t="s">
-        <v>453</v>
+      <c r="H85" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I85" s="4">
         <v>29623316906.279999</v>
@@ -18926,14 +18734,14 @@
       <c r="K85" s="4">
         <v>29623316906.279999</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="13">
         <v>44925</v>
       </c>
-      <c r="M85" s="19"/>
-      <c r="N85" s="19">
+      <c r="M85" s="13"/>
+      <c r="N85" s="13">
         <v>44952</v>
       </c>
-      <c r="O85" s="19">
+      <c r="O85" s="13">
         <v>45030</v>
       </c>
       <c r="P85" s="4">
@@ -18944,18 +18752,18 @@
       </c>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>92</v>
@@ -18966,8 +18774,8 @@
       <c r="G86" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H86" s="22" t="s">
-        <v>467</v>
+      <c r="H86" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I86" s="4">
         <v>30461715692</v>
@@ -18978,14 +18786,14 @@
       <c r="K86" s="4">
         <v>30461715692</v>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="13">
         <v>45064</v>
       </c>
-      <c r="M86" s="19"/>
-      <c r="N86" s="19">
+      <c r="M86" s="13"/>
+      <c r="N86" s="13">
         <v>45202</v>
       </c>
-      <c r="O86" s="19">
+      <c r="O86" s="13">
         <v>45289</v>
       </c>
       <c r="P86" s="4">
@@ -18996,18 +18804,18 @@
       </c>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>66</v>
@@ -19019,7 +18827,7 @@
         <v>68</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I87" s="4">
         <v>17454000000</v>
@@ -19030,14 +18838,14 @@
       <c r="K87" s="4">
         <v>17761000000</v>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="13">
         <v>45154</v>
       </c>
-      <c r="M87" s="19"/>
-      <c r="N87" s="19">
+      <c r="M87" s="13"/>
+      <c r="N87" s="13">
         <v>45428</v>
       </c>
-      <c r="O87" s="19">
+      <c r="O87" s="13">
         <v>45317</v>
       </c>
       <c r="P87" s="4">
@@ -19048,18 +18856,18 @@
       </c>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>66</v>
@@ -19071,7 +18879,7 @@
         <v>68</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I88" s="4">
         <v>8419333809</v>
@@ -19082,14 +18890,14 @@
       <c r="K88" s="4">
         <v>9930787094</v>
       </c>
-      <c r="L88" s="19">
+      <c r="L88" s="13">
         <v>45154</v>
       </c>
-      <c r="M88" s="19"/>
-      <c r="N88" s="19">
+      <c r="M88" s="13"/>
+      <c r="N88" s="13">
         <v>45281</v>
       </c>
-      <c r="O88" s="19">
+      <c r="O88" s="13">
         <v>45328</v>
       </c>
       <c r="P88" s="4">
@@ -19100,30 +18908,30 @@
       </c>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H89" s="22" t="s">
-        <v>462</v>
+      <c r="H89" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I89" s="4">
         <v>94461519789</v>
@@ -19134,14 +18942,14 @@
       <c r="K89" s="4">
         <v>94461519789</v>
       </c>
-      <c r="L89" s="19">
+      <c r="L89" s="13">
         <v>45290</v>
       </c>
-      <c r="M89" s="19"/>
-      <c r="N89" s="19">
+      <c r="M89" s="13"/>
+      <c r="N89" s="13">
         <v>45369</v>
       </c>
-      <c r="O89" s="19">
+      <c r="O89" s="13">
         <v>45539</v>
       </c>
       <c r="P89" s="4">
@@ -19152,30 +18960,30 @@
       </c>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I90" s="4">
         <v>3362968761</v>
@@ -19186,14 +18994,14 @@
       <c r="K90" s="4">
         <v>4543549645</v>
       </c>
-      <c r="L90" s="19">
+      <c r="L90" s="13">
         <v>45596</v>
       </c>
-      <c r="M90" s="19"/>
-      <c r="N90" s="19">
+      <c r="M90" s="13"/>
+      <c r="N90" s="13">
         <v>45649</v>
       </c>
-      <c r="O90" s="19">
+      <c r="O90" s="13">
         <v>45721</v>
       </c>
       <c r="P90" s="4">
@@ -19204,18 +19012,18 @@
       </c>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" spans="1:18" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>66</v>
@@ -19227,7 +19035,7 @@
         <v>68</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I91" s="4">
         <v>23600000000</v>
@@ -19238,14 +19046,14 @@
       <c r="K91" s="4">
         <v>24518488200</v>
       </c>
-      <c r="L91" s="19">
+      <c r="L91" s="13">
         <v>45861</v>
       </c>
-      <c r="M91" s="19"/>
-      <c r="N91" s="19">
+      <c r="M91" s="13"/>
+      <c r="N91" s="13">
         <v>45916</v>
       </c>
-      <c r="O91" s="19">
+      <c r="O91" s="13">
         <v>45965</v>
       </c>
       <c r="P91" s="4">
@@ -19256,18 +19064,18 @@
       </c>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>66</v>
@@ -19279,7 +19087,7 @@
         <v>68</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I92" s="4">
         <v>30000000000</v>
@@ -19290,14 +19098,14 @@
       <c r="K92" s="4">
         <v>31068885740</v>
       </c>
-      <c r="L92" s="19">
+      <c r="L92" s="13">
         <v>45861</v>
       </c>
-      <c r="M92" s="19"/>
-      <c r="N92" s="19">
+      <c r="M92" s="13"/>
+      <c r="N92" s="13">
         <v>45904</v>
       </c>
-      <c r="O92" s="19">
+      <c r="O92" s="13">
         <v>45976</v>
       </c>
       <c r="P92" s="4">
@@ -19308,15 +19116,15 @@
       </c>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
@@ -19329,7 +19137,7 @@
         <v>68</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I93" s="4">
         <v>30000000000</v>
@@ -19340,14 +19148,14 @@
       <c r="K93" s="4">
         <v>30899136874.049999</v>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="13">
         <v>45861</v>
       </c>
-      <c r="M93" s="19"/>
-      <c r="N93" s="19">
+      <c r="M93" s="13"/>
+      <c r="N93" s="13">
         <v>45926</v>
       </c>
-      <c r="O93" s="19">
+      <c r="O93" s="13">
         <v>45980</v>
       </c>
       <c r="P93" s="4">
@@ -19358,15 +19166,15 @@
       </c>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
@@ -19378,8 +19186,8 @@
       <c r="G94" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H94" s="22" t="s">
-        <v>462</v>
+      <c r="H94" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I94" s="4">
         <v>172253454</v>
@@ -19390,14 +19198,14 @@
       <c r="K94" s="4">
         <v>172253454</v>
       </c>
-      <c r="L94" s="19">
+      <c r="L94" s="13">
         <v>45715</v>
       </c>
-      <c r="M94" s="19"/>
-      <c r="N94" s="19">
+      <c r="M94" s="13"/>
+      <c r="N94" s="13">
         <v>46008</v>
       </c>
-      <c r="O94" s="19">
+      <c r="O94" s="13">
         <v>46014</v>
       </c>
       <c r="P94" s="4">
@@ -19408,18 +19216,18 @@
       </c>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>212</v>
@@ -19430,8 +19238,8 @@
       <c r="G95" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H95" s="23" t="s">
-        <v>467</v>
+      <c r="H95" s="16" t="s">
+        <v>456</v>
       </c>
       <c r="I95" s="4">
         <v>511865531</v>
@@ -19442,14 +19250,14 @@
       <c r="K95" s="4">
         <v>711865531</v>
       </c>
-      <c r="L95" s="19">
+      <c r="L95" s="13">
         <v>45756</v>
       </c>
-      <c r="M95" s="19"/>
-      <c r="N95" s="19">
+      <c r="M95" s="13"/>
+      <c r="N95" s="13">
         <v>45775</v>
       </c>
-      <c r="O95" s="19">
+      <c r="O95" s="13">
         <v>45922</v>
       </c>
       <c r="P95" s="4">
@@ -19460,15 +19268,15 @@
       </c>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
@@ -19480,8 +19288,8 @@
       <c r="G96" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H96" s="22" t="s">
-        <v>507</v>
+      <c r="H96" s="15" t="s">
+        <v>496</v>
       </c>
       <c r="I96" s="4">
         <v>386045990.94</v>
@@ -19492,14 +19300,14 @@
       <c r="K96" s="4">
         <v>586045990.94000006</v>
       </c>
-      <c r="L96" s="19">
+      <c r="L96" s="13">
         <v>45917</v>
       </c>
-      <c r="M96" s="19"/>
-      <c r="N96" s="19">
+      <c r="M96" s="13"/>
+      <c r="N96" s="13">
         <v>45938</v>
       </c>
-      <c r="O96" s="19"/>
+      <c r="O96" s="13"/>
       <c r="P96" s="4">
         <v>0</v>
       </c>
@@ -19508,18 +19316,18 @@
       </c>
       <c r="R96" s="3"/>
     </row>
-    <row r="97" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>92</v>
@@ -19530,8 +19338,8 @@
       <c r="G97" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H97" s="22" t="s">
-        <v>462</v>
+      <c r="H97" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I97" s="4">
         <v>59900815918</v>
@@ -19542,14 +19350,14 @@
       <c r="K97" s="4">
         <v>59900815918</v>
       </c>
-      <c r="L97" s="19">
+      <c r="L97" s="13">
         <v>45911</v>
       </c>
-      <c r="M97" s="19"/>
-      <c r="N97" s="19">
+      <c r="M97" s="13"/>
+      <c r="N97" s="13">
         <v>45922</v>
       </c>
-      <c r="O97" s="19">
+      <c r="O97" s="13">
         <v>45974</v>
       </c>
       <c r="P97" s="4">
@@ -19560,30 +19368,30 @@
       </c>
       <c r="R97" s="3"/>
     </row>
-    <row r="98" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H98" s="22" t="s">
-        <v>462</v>
+      <c r="H98" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I98" s="4">
         <v>28121067144</v>
@@ -19594,14 +19402,14 @@
       <c r="K98" s="4">
         <v>28263067144</v>
       </c>
-      <c r="L98" s="19">
+      <c r="L98" s="13">
         <v>45861</v>
       </c>
-      <c r="M98" s="19"/>
-      <c r="N98" s="19">
+      <c r="M98" s="13"/>
+      <c r="N98" s="13">
         <v>45882</v>
       </c>
-      <c r="O98" s="19">
+      <c r="O98" s="13">
         <v>45926</v>
       </c>
       <c r="P98" s="4">
@@ -19612,18 +19420,18 @@
       </c>
       <c r="R98" s="3"/>
     </row>
-    <row r="99" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>66</v>
@@ -19635,7 +19443,7 @@
         <v>207</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I99" s="4">
         <v>1989520159</v>
@@ -19646,14 +19454,14 @@
       <c r="K99" s="4">
         <v>2825408806</v>
       </c>
-      <c r="L99" s="19">
+      <c r="L99" s="13">
         <v>44078</v>
       </c>
-      <c r="M99" s="19"/>
-      <c r="N99" s="19">
+      <c r="M99" s="13"/>
+      <c r="N99" s="13">
         <v>44176</v>
       </c>
-      <c r="O99" s="19"/>
+      <c r="O99" s="13"/>
       <c r="P99" s="4">
         <v>98.57</v>
       </c>
@@ -19662,18 +19470,18 @@
       </c>
       <c r="R99" s="3"/>
     </row>
-    <row r="100" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>66</v>
@@ -19685,7 +19493,7 @@
         <v>207</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I100" s="4">
         <v>4869404585</v>
@@ -19696,14 +19504,14 @@
       <c r="K100" s="4">
         <v>5039787989</v>
       </c>
-      <c r="L100" s="19">
+      <c r="L100" s="13">
         <v>44384</v>
       </c>
-      <c r="M100" s="19"/>
-      <c r="N100" s="19">
+      <c r="M100" s="13"/>
+      <c r="N100" s="13">
         <v>44407</v>
       </c>
-      <c r="O100" s="19">
+      <c r="O100" s="13">
         <v>44560</v>
       </c>
       <c r="P100" s="4">
@@ -19714,30 +19522,30 @@
       </c>
       <c r="R100" s="3"/>
     </row>
-    <row r="101" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I101" s="4">
         <v>2644584337.2600002</v>
@@ -19748,14 +19556,14 @@
       <c r="K101" s="4">
         <v>2644584337.2600002</v>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="13">
         <v>44456</v>
       </c>
-      <c r="M101" s="19"/>
-      <c r="N101" s="19">
+      <c r="M101" s="13"/>
+      <c r="N101" s="13">
         <v>44489</v>
       </c>
-      <c r="O101" s="19">
+      <c r="O101" s="13">
         <v>44859</v>
       </c>
       <c r="P101" s="4">
@@ -19766,30 +19574,30 @@
       </c>
       <c r="R101" s="3"/>
     </row>
-    <row r="102" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I102" s="4">
         <v>6578630543.6700001</v>
@@ -19800,14 +19608,14 @@
       <c r="K102" s="4">
         <v>6578630543.6700001</v>
       </c>
-      <c r="L102" s="19">
+      <c r="L102" s="13">
         <v>44559</v>
       </c>
-      <c r="M102" s="19"/>
-      <c r="N102" s="19">
+      <c r="M102" s="13"/>
+      <c r="N102" s="13">
         <v>44566</v>
       </c>
-      <c r="O102" s="19">
+      <c r="O102" s="13">
         <v>44697</v>
       </c>
       <c r="P102" s="4">
@@ -19818,18 +19626,18 @@
       </c>
       <c r="R102" s="3"/>
     </row>
-    <row r="103" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>92</v>
@@ -19841,7 +19649,7 @@
         <v>207</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I103" s="4">
         <v>6853127845.6300001</v>
@@ -19852,14 +19660,14 @@
       <c r="K103" s="4">
         <v>6853127845.6300001</v>
       </c>
-      <c r="L103" s="19">
+      <c r="L103" s="13">
         <v>45216</v>
       </c>
-      <c r="M103" s="19"/>
-      <c r="N103" s="19">
+      <c r="M103" s="13"/>
+      <c r="N103" s="13">
         <v>45219</v>
       </c>
-      <c r="O103" s="19">
+      <c r="O103" s="13">
         <v>45286</v>
       </c>
       <c r="P103" s="4">
@@ -19870,28 +19678,28 @@
       </c>
       <c r="R103" s="3"/>
     </row>
-    <row r="104" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="H104" s="21" t="s">
-        <v>507</v>
+        <v>872</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>496</v>
       </c>
       <c r="I104" s="4">
         <v>36139210439</v>
@@ -19902,14 +19710,14 @@
       <c r="K104" s="4">
         <v>36139210439</v>
       </c>
-      <c r="L104" s="19">
+      <c r="L104" s="13">
         <v>46080</v>
       </c>
-      <c r="M104" s="19"/>
-      <c r="N104" s="19">
+      <c r="M104" s="13"/>
+      <c r="N104" s="13">
         <v>46091</v>
       </c>
-      <c r="O104" s="19"/>
+      <c r="O104" s="13"/>
       <c r="P104" s="4">
         <v>0</v>
       </c>
@@ -19930,18 +19738,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20089,18 +19897,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA423ED4-21A6-41DF-89D7-6CD27D950967}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8937D50-EA8A-4E8E-9144-993F62C56134}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8937D50-EA8A-4E8E-9144-993F62C56134}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA423ED4-21A6-41DF-89D7-6CD27D950967}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
